--- a/Gehaltsrechner_Karimov.xlsx
+++ b/Gehaltsrechner_Karimov.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Права и риски" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Мои данные" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Год" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Сверка с расчёткой" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -172,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -274,6 +275,7 @@
     <xf numFmtId="164" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -348,6 +350,32 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -736,7 +764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -788,7 +816,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>График месяца: ND / TD / FREI, статус (Arbeit / Urlaub / Krank), «x» = Eingesprungen. Август 2026 заполнен.</t>
+          <t>График месяца: ND / TD / FREI, статус (Arbeit / Urlaub / Krank), «x» = Eingesprungen. Август 2026 заполнен по факту: 18 смен = 216 ч.</t>
         </is>
       </c>
     </row>
@@ -876,322 +904,331 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Сверка с расчёткой</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Реальные Lohnabrechnung 07/2026 и 08/2026, разобранные построчно, и проверка каждой суммы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>ВАЖНО ПРО ФОРМАТ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Время смен — это ЧИСЛА</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>20 = 20:00, 8 = 08:00, 6,5 = 06:30. Так сделано специально: Numbers на iPhone/Mac ломает формулы с настоящими значениями времени.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Numbers убирает подсветку</t>
+          <t>Время смен — это ЧИСЛА</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Цветные предупреждения Numbers удаляет. Поэтому все предупреждения продублированы ТЕКСТОМ в последней колонке Dienstplan и на листе «Контроль ArbZG».</t>
+          <t>20 = 20:00, 8 = 08:00, 6,5 = 06:30. Так сделано специально: Numbers на iPhone/Mac ломает формулы с настоящими значениями времени.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="B19" s="4" t="inlineStr">
         <is>
+          <t>Numbers убирает подсветку</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Цветные предупреждения Numbers удаляет. Поэтому все предупреждения продублированы ТЕКСТОМ в последней колонке Dienstplan и на листе «Контроль ArbZG».</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>Если что-то показывает ошибку</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Открой в Excel, Google Sheets или LibreOffice — там работает всё. В Numbers формулы тоже работают, но подсветка и выпадающие списки пропадают.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>ЧТО ГОВОРИТ ДОГОВОР (§ 3 Vergütung)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Часовая ставка</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>27,00 € брутто (§ 3 Abs. 1)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Оклад в месяц</t>
+          <t>Часовая ставка</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>4.676,40 € брутто → норма 4.676,40 / 27,00 = 173,20 ч/мес</t>
+          <t>27,00 € брутто (§ 3 Abs. 1)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Рабочее время</t>
+          <t>Оклад в месяц</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>40 ч в неделю, пятидневка, БЕЗ учёта перерывов (§ 2 Abs. 1)</t>
+          <t>4.676,40 € брутто → норма 4.676,40 / 27,00 = 173,20 ч/мес</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Ночь 20:00–06:00</t>
+          <t>Рабочее время</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>+25 % (§ 3 Abs. 2 a)</t>
+          <t>40 ч в неделю, пятидневка, БЕЗ учёта перерывов (§ 2 Abs. 1)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Воскресенье 00:00–24:00</t>
+          <t>Ночь 20:00–06:00</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>+50 % (§ 3 Abs. 2 b)</t>
+          <t>+25 % (§ 3 Abs. 2 a)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Праздник с отгулом (mit FZA)</t>
+          <t>Воскресенье 00:00–24:00</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>+35 % (§ 3 Abs. 2 c)</t>
+          <t>+50 % (§ 3 Abs. 2 b)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Праздник без отгула (ohne FZA)</t>
+          <t>Праздник с отгулом (mit FZA)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>+135 % (§ 3 Abs. 2 d)</t>
+          <t>+35 % (§ 3 Abs. 2 c)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="B29" s="4" t="inlineStr">
         <is>
+          <t>Праздник без отгула (ohne FZA)</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+135 % (§ 3 Abs. 2 d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
           <t>Совпадение надбавок</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Платится ТОЛЬКО САМАЯ ВЫСОКАЯ. Ночь в воскресенье = 50 %, не 75 %.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
+    <row r="31" ht="26" customHeight="1">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Твои смены</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>ND 20:00–08:00 = 12 ч, из них 10 ч ночных (20:00–06:00) и 2 ч обычных (06:00–08:00). TD 08:00–20:00 = 12 ч, ночных 0.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="39" customHeight="1">
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="39" customHeight="1">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Переработка</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>§ 2 Abs. 3: первые 8 ч/мес включены в оклад. Работодатель на практике оплачивает максимум 60 ч/мес, остальное переносит в следующий месяц отгулами — в договоре этого правила НЕТ, см. лист «Права и риски».</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Выплата</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>15-го числа следующего месяца (§ 3 Abs. 3)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="B33" s="4" t="inlineStr">
         <is>
+          <t>Выплата</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>15-го числа следующего месяца (§ 3 Abs. 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
           <t>Срок претензий</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>3 месяца — § 14 Ausschlussfrist. Пропустил — право пропало.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>НАЛОГИ И ВЗНОСЫ</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="26" customHeight="1">
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>§ 3b EStG</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Надбавки за ночь/воскресенье/праздник свободны от подоходного налога: ночь до 25 %, воскресенье до 50 %, праздник до 125 % (01.05, 25./26.12 и 24.12 с 14:00 — до 150 %). База — максимум 50 €/ч.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>§ 1 Abs. 1 SvEV</t>
+          <t>§ 3b EStG</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>От соцвзносов надбавки свободны только с базы 25,00 €/ч. Ставка 27,00 € → часть надбавки, посчитанная с 2,00 €/ч, взносами облагается. Файл делит автоматически.</t>
+          <t>Надбавки за ночь/воскресенье/праздник свободны от подоходного налога: ночь до 25 %, воскресенье до 50 %, праздник до 125 % (01.05, 25./26.12 и 24.12 с 14:00 — до 150 %). База — максимум 50 €/ч.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Отпуск и больничный</t>
+          <t>§ 1 Abs. 1 SvEV</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Надбавки, выплаченные за дни отпуска/болезни, налогом ОБЛАГАЮТСЯ — § 3b требует фактической работы. Ставь статус Urlaub/Krank.</t>
+          <t>От соцвзносов надбавки свободны только с базы 25,00 €/ч. Ставка 27,00 € → часть надбавки, посчитанная с 2,00 €/ч, взносами облагается. Файл делит автоматически.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
       <c r="B39" s="4" t="inlineStr">
         <is>
+          <t>Отпуск и больничный</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Надбавки, выплаченные за дни отпуска/болезни, налогом ОБЛАГАЮТСЯ — § 3b требует фактической работы. Ставь статус Urlaub/Krank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="B40" s="4" t="inlineStr">
+        <is>
           <t>Налоговый класс 3, 1 ребёнок</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Считается по Splittingtarif. Ребёнок с 2025 г. → доплата бездетных в Pflegeversicherung (0,6 %) больше НЕ удерживается — проверь это в Lohnabrechnung.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>ТОЧНОСТЬ</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Часы, надбавки, брутто</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>Точно — по формулам договора.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Соцвзносы</t>
+          <t>Часы, надбавки, брутто</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Точно — ставки и предельные базы 2026.</t>
+          <t>Точно — по формулам договора.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Подоходный налог</t>
+          <t>Соцвзносы</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Оценка ±несколько евро. Классы 5 и 6 не поддерживаются.</t>
+          <t>Точно — ставки и предельные базы 2026.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="B45" s="4" t="inlineStr">
         <is>
+          <t>Подоходный налог</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Оценка ±несколько евро. Классы 5 и 6 не поддерживаются.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
           <t>Нетто</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Оценка. Официальный документ — Lohnabrechnung. Этот файл нужен, чтобы её проверить.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Файл — вспомогательный инструмент, не юридическая консультация. При споре: профсоюз ver.di или Fachanwalt für Arbeitsrecht.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="C17:F17"/>
+  <mergeCells count="39">
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="C8:F8"/>
@@ -1199,34 +1236,38 @@
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C19:F19"/>
-    <mergeCell ref="A21:F21"/>
     <mergeCell ref="C37:F37"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C18:F18"/>
+    <mergeCell ref="A42:F42"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="C34:F34"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="C30:F30"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="C33:F33"/>
-    <mergeCell ref="A35:F35"/>
     <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C42:F42"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="C45:F45"/>
+    <mergeCell ref="C20:F20"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C44:F44"/>
-    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C40:F40"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C31:F31"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C43:F43"/>
+    <mergeCell ref="C46:F46"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C36:F36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1309,200 +1350,200 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="63" t="inlineStr">
+      <c r="B5" s="64" t="inlineStr">
         <is>
           <t>Январь</t>
         </is>
       </c>
       <c r="C5" s="31" t="n"/>
-      <c r="D5" s="64" t="n"/>
-      <c r="E5" s="64" t="n"/>
-      <c r="F5" s="64" t="n"/>
-      <c r="G5" s="64" t="n"/>
-      <c r="H5" s="64" t="n"/>
+      <c r="D5" s="65" t="n"/>
+      <c r="E5" s="65" t="n"/>
+      <c r="F5" s="65" t="n"/>
+      <c r="G5" s="65" t="n"/>
+      <c r="H5" s="65" t="n"/>
       <c r="I5" s="31" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="63" t="inlineStr">
+      <c r="B6" s="64" t="inlineStr">
         <is>
           <t>Февраль</t>
         </is>
       </c>
       <c r="C6" s="31" t="n"/>
-      <c r="D6" s="64" t="n"/>
-      <c r="E6" s="64" t="n"/>
-      <c r="F6" s="64" t="n"/>
-      <c r="G6" s="64" t="n"/>
-      <c r="H6" s="64" t="n"/>
+      <c r="D6" s="65" t="n"/>
+      <c r="E6" s="65" t="n"/>
+      <c r="F6" s="65" t="n"/>
+      <c r="G6" s="65" t="n"/>
+      <c r="H6" s="65" t="n"/>
       <c r="I6" s="31" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="63" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>Март</t>
         </is>
       </c>
       <c r="C7" s="31" t="n"/>
-      <c r="D7" s="64" t="n"/>
-      <c r="E7" s="64" t="n"/>
-      <c r="F7" s="64" t="n"/>
-      <c r="G7" s="64" t="n"/>
-      <c r="H7" s="64" t="n"/>
+      <c r="D7" s="65" t="n"/>
+      <c r="E7" s="65" t="n"/>
+      <c r="F7" s="65" t="n"/>
+      <c r="G7" s="65" t="n"/>
+      <c r="H7" s="65" t="n"/>
       <c r="I7" s="31" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="63" t="inlineStr">
+      <c r="B8" s="64" t="inlineStr">
         <is>
           <t>Апрель</t>
         </is>
       </c>
       <c r="C8" s="31" t="n"/>
-      <c r="D8" s="64" t="n"/>
-      <c r="E8" s="64" t="n"/>
-      <c r="F8" s="64" t="n"/>
-      <c r="G8" s="64" t="n"/>
-      <c r="H8" s="64" t="n"/>
+      <c r="D8" s="65" t="n"/>
+      <c r="E8" s="65" t="n"/>
+      <c r="F8" s="65" t="n"/>
+      <c r="G8" s="65" t="n"/>
+      <c r="H8" s="65" t="n"/>
       <c r="I8" s="31" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="63" t="inlineStr">
+      <c r="B9" s="64" t="inlineStr">
         <is>
           <t>Май</t>
         </is>
       </c>
       <c r="C9" s="31" t="n"/>
-      <c r="D9" s="64" t="n"/>
-      <c r="E9" s="64" t="n"/>
-      <c r="F9" s="64" t="n"/>
-      <c r="G9" s="64" t="n"/>
-      <c r="H9" s="64" t="n"/>
+      <c r="D9" s="65" t="n"/>
+      <c r="E9" s="65" t="n"/>
+      <c r="F9" s="65" t="n"/>
+      <c r="G9" s="65" t="n"/>
+      <c r="H9" s="65" t="n"/>
       <c r="I9" s="31" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="63" t="inlineStr">
+      <c r="B10" s="64" t="inlineStr">
         <is>
           <t>Июнь</t>
         </is>
       </c>
       <c r="C10" s="31" t="n"/>
-      <c r="D10" s="64" t="n"/>
-      <c r="E10" s="64" t="n"/>
-      <c r="F10" s="64" t="n"/>
-      <c r="G10" s="64" t="n"/>
-      <c r="H10" s="64" t="n"/>
+      <c r="D10" s="65" t="n"/>
+      <c r="E10" s="65" t="n"/>
+      <c r="F10" s="65" t="n"/>
+      <c r="G10" s="65" t="n"/>
+      <c r="H10" s="65" t="n"/>
       <c r="I10" s="31" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="63" t="inlineStr">
+      <c r="B11" s="64" t="inlineStr">
         <is>
           <t>Июль</t>
         </is>
       </c>
       <c r="C11" s="31" t="n"/>
-      <c r="D11" s="64" t="n"/>
-      <c r="E11" s="64" t="n"/>
-      <c r="F11" s="64" t="n"/>
-      <c r="G11" s="64" t="n"/>
-      <c r="H11" s="64" t="n"/>
+      <c r="D11" s="65" t="n"/>
+      <c r="E11" s="65" t="n"/>
+      <c r="F11" s="65" t="n"/>
+      <c r="G11" s="65" t="n"/>
+      <c r="H11" s="65" t="n"/>
       <c r="I11" s="31" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="63" t="inlineStr">
+      <c r="B12" s="64" t="inlineStr">
         <is>
           <t>Август</t>
         </is>
       </c>
       <c r="C12" s="31" t="n"/>
-      <c r="D12" s="64" t="n"/>
-      <c r="E12" s="64" t="n"/>
-      <c r="F12" s="64" t="n"/>
-      <c r="G12" s="64" t="n"/>
-      <c r="H12" s="64" t="n"/>
+      <c r="D12" s="65" t="n"/>
+      <c r="E12" s="65" t="n"/>
+      <c r="F12" s="65" t="n"/>
+      <c r="G12" s="65" t="n"/>
+      <c r="H12" s="65" t="n"/>
       <c r="I12" s="31" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="63" t="inlineStr">
+      <c r="B13" s="64" t="inlineStr">
         <is>
           <t>Сентябрь</t>
         </is>
       </c>
       <c r="C13" s="31" t="n"/>
-      <c r="D13" s="64" t="n"/>
-      <c r="E13" s="64" t="n"/>
-      <c r="F13" s="64" t="n"/>
-      <c r="G13" s="64" t="n"/>
-      <c r="H13" s="64" t="n"/>
+      <c r="D13" s="65" t="n"/>
+      <c r="E13" s="65" t="n"/>
+      <c r="F13" s="65" t="n"/>
+      <c r="G13" s="65" t="n"/>
+      <c r="H13" s="65" t="n"/>
       <c r="I13" s="31" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="63" t="inlineStr">
+      <c r="B14" s="64" t="inlineStr">
         <is>
           <t>Октябрь</t>
         </is>
       </c>
       <c r="C14" s="31" t="n"/>
-      <c r="D14" s="64" t="n"/>
-      <c r="E14" s="64" t="n"/>
-      <c r="F14" s="64" t="n"/>
-      <c r="G14" s="64" t="n"/>
-      <c r="H14" s="64" t="n"/>
+      <c r="D14" s="65" t="n"/>
+      <c r="E14" s="65" t="n"/>
+      <c r="F14" s="65" t="n"/>
+      <c r="G14" s="65" t="n"/>
+      <c r="H14" s="65" t="n"/>
       <c r="I14" s="31" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="63" t="inlineStr">
+      <c r="B15" s="64" t="inlineStr">
         <is>
           <t>Ноябрь</t>
         </is>
       </c>
       <c r="C15" s="31" t="n"/>
-      <c r="D15" s="64" t="n"/>
-      <c r="E15" s="64" t="n"/>
-      <c r="F15" s="64" t="n"/>
-      <c r="G15" s="64" t="n"/>
-      <c r="H15" s="64" t="n"/>
+      <c r="D15" s="65" t="n"/>
+      <c r="E15" s="65" t="n"/>
+      <c r="F15" s="65" t="n"/>
+      <c r="G15" s="65" t="n"/>
+      <c r="H15" s="65" t="n"/>
       <c r="I15" s="31" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="63" t="inlineStr">
+      <c r="B16" s="64" t="inlineStr">
         <is>
           <t>Декабрь</t>
         </is>
       </c>
       <c r="C16" s="31" t="n"/>
-      <c r="D16" s="64" t="n"/>
-      <c r="E16" s="64" t="n"/>
-      <c r="F16" s="64" t="n"/>
-      <c r="G16" s="64" t="n"/>
-      <c r="H16" s="64" t="n"/>
+      <c r="D16" s="65" t="n"/>
+      <c r="E16" s="65" t="n"/>
+      <c r="F16" s="65" t="n"/>
+      <c r="G16" s="65" t="n"/>
+      <c r="H16" s="65" t="n"/>
       <c r="I16" s="31" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="65" t="inlineStr">
+      <c r="B17" s="66" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C17" s="66">
+      <c r="C17" s="67">
         <f>SUM(C5:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="67">
+      <c r="D17" s="68">
         <f>SUM(D5:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="67">
+      <c r="E17" s="68">
         <f>SUM(E5:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="67">
+      <c r="F17" s="68">
         <f>SUM(F5:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="67">
+      <c r="G17" s="68">
         <f>SUM(G5:G16)</f>
         <v/>
       </c>
-      <c r="H17" s="67">
+      <c r="H17" s="68">
         <f>SUM(H5:H16)</f>
         <v/>
       </c>
@@ -1557,6 +1598,1106 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B22:I22"/>
     <mergeCell ref="B23:I23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>СВЕРКА С РЕАЛЬНОЙ РАСЧЁТКОЙ / ABGLEICH MIT DER LOHNABRECHNUNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Данные взяты дословно из Verdienstnachweis 07/2026 и 08/2026 (Constantia Intensivpflege GmbH). Колонка «Проверка» пересчитывает сумму формулой — если совпало, строка верна.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="19" customHeight="1">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>АВГУСТ 2026 — Abrechnung vom 09.09.2026, выплата 14.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Строка расчётки</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Часы</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Ставка</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>В расчётке</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="64" t="inlineStr">
+        <is>
+          <t>101 Stundenlohn</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="n">
+        <v>168</v>
+      </c>
+      <c r="D5" s="69" t="n">
+        <v>27</v>
+      </c>
+      <c r="E5" s="29" t="inlineStr"/>
+      <c r="F5" s="69" t="n">
+        <v>4536</v>
+      </c>
+      <c r="G5" s="70">
+        <f>ROUND($C5*$D5*IF($E5="",1,$E5),2)</f>
+        <v/>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Норма месяца (Zeitlohn Stunden)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="64" t="inlineStr">
+        <is>
+          <t>103 Überstdgrundvergütung</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="n">
+        <v>48</v>
+      </c>
+      <c r="D6" s="69" t="n">
+        <v>27</v>
+      </c>
+      <c r="E6" s="29" t="inlineStr"/>
+      <c r="F6" s="69" t="n">
+        <v>1296</v>
+      </c>
+      <c r="G6" s="70">
+        <f>ROUND($C6*$D6*IF($E6="",1,$E6),2)</f>
+        <v/>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Переработка. Та же ставка, надбавки за переработку нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t>114 Nacht 25% frei</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>132</v>
+      </c>
+      <c r="D7" s="69" t="n">
+        <v>27</v>
+      </c>
+      <c r="E7" s="71" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F7" s="69" t="n">
+        <v>891</v>
+      </c>
+      <c r="G7" s="70">
+        <f>ROUND($C7*$D7*IF($E7="",1,$E7),2)</f>
+        <v/>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Ночная надбавка. F F = без налога и без взносов</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="64" t="inlineStr">
+        <is>
+          <t>115 Sonntag 50% frei</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="n">
+        <v>44</v>
+      </c>
+      <c r="D8" s="69" t="n">
+        <v>27</v>
+      </c>
+      <c r="E8" s="71" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="69" t="n">
+        <v>594</v>
+      </c>
+      <c r="G8" s="70">
+        <f>ROUND($C8*$D8*IF($E8="",1,$E8),2)</f>
+        <v/>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Воскресная надбавка. F F = без налога и без взносов</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="72" t="inlineStr">
+        <is>
+          <t>Gesamt-Brutto</t>
+        </is>
+      </c>
+      <c r="C9" s="73" t="n"/>
+      <c r="D9" s="73" t="n"/>
+      <c r="E9" s="73" t="n"/>
+      <c r="F9" s="68" t="n">
+        <v>7317</v>
+      </c>
+      <c r="G9" s="74">
+        <f>SUM($F$5:$F$8)</f>
+        <v/>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Сумма четырёх строк выше</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="64" t="inlineStr">
+        <is>
+          <t>Steuer-Brutto</t>
+        </is>
+      </c>
+      <c r="C10" s="73" t="n"/>
+      <c r="D10" s="73" t="n"/>
+      <c r="E10" s="73" t="n"/>
+      <c r="F10" s="69" t="n">
+        <v>5832</v>
+      </c>
+      <c r="G10" s="73" t="n"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>4.536 + 1.296. Надбавки 891 + 594 в базу не входят — § 3b EStG</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="64" t="inlineStr">
+        <is>
+          <t>Lohnsteuer</t>
+        </is>
+      </c>
+      <c r="C11" s="73" t="n"/>
+      <c r="D11" s="73" t="n"/>
+      <c r="E11" s="73" t="n"/>
+      <c r="F11" s="69" t="n">
+        <v>-587.66</v>
+      </c>
+      <c r="G11" s="73" t="n"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Класс 3, 1 ребёнок</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="64" t="inlineStr">
+        <is>
+          <t>KV-Beitrag</t>
+        </is>
+      </c>
+      <c r="C12" s="73" t="n"/>
+      <c r="D12" s="73" t="n"/>
+      <c r="E12" s="73" t="n"/>
+      <c r="F12" s="69" t="n">
+        <v>-511.21</v>
+      </c>
+      <c r="G12" s="73" t="n"/>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>5.812,50 € (потолок) × 8,795 % = (14,6 % + 2,99 %) / 2 → доп. взнос AOK BW = 2,99 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="64" t="inlineStr">
+        <is>
+          <t>RV-Beitrag</t>
+        </is>
+      </c>
+      <c r="C13" s="73" t="n"/>
+      <c r="D13" s="73" t="n"/>
+      <c r="E13" s="73" t="n"/>
+      <c r="F13" s="69" t="n">
+        <v>-542.38</v>
+      </c>
+      <c r="G13" s="73" t="n"/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>5.832,00 € × 9,3 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="64" t="inlineStr">
+        <is>
+          <t>AV-Beitrag</t>
+        </is>
+      </c>
+      <c r="C14" s="73" t="n"/>
+      <c r="D14" s="73" t="n"/>
+      <c r="E14" s="73" t="n"/>
+      <c r="F14" s="69" t="n">
+        <v>-75.81999999999999</v>
+      </c>
+      <c r="G14" s="73" t="n"/>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>5.832,00 € × 1,3 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="64" t="inlineStr">
+        <is>
+          <t>PV-Beitrag</t>
+        </is>
+      </c>
+      <c r="C15" s="73" t="n"/>
+      <c r="D15" s="73" t="n"/>
+      <c r="E15" s="73" t="n"/>
+      <c r="F15" s="69" t="n">
+        <v>-104.63</v>
+      </c>
+      <c r="G15" s="73" t="n"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>5.812,50 € × 1,8 %. Доплата бездетным 0,6 % НЕ удержана — верно, ребёнок учтён («1»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="72" t="inlineStr">
+        <is>
+          <t>Netto-Verdienst</t>
+        </is>
+      </c>
+      <c r="C16" s="73" t="n"/>
+      <c r="D16" s="73" t="n"/>
+      <c r="E16" s="73" t="n"/>
+      <c r="F16" s="68" t="n">
+        <v>5495.3</v>
+      </c>
+      <c r="G16" s="73" t="n"/>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>Всё, что осталось после налога и взносов</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="64" t="inlineStr">
+        <is>
+          <t>Abschlag / Vorschuss</t>
+        </is>
+      </c>
+      <c r="C17" s="73" t="n"/>
+      <c r="D17" s="73" t="n"/>
+      <c r="E17" s="73" t="n"/>
+      <c r="F17" s="69" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="G17" s="73" t="n"/>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Аванс, полученный раньше</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="64" t="inlineStr">
+        <is>
+          <t>aus NB 07/2026</t>
+        </is>
+      </c>
+      <c r="C18" s="73" t="n"/>
+      <c r="D18" s="73" t="n"/>
+      <c r="E18" s="73" t="n"/>
+      <c r="F18" s="69" t="n">
+        <v>117</v>
+      </c>
+      <c r="G18" s="73" t="n"/>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Доплата ночных за ИЮЛЬ — см. раздел ниже. К августу отношения не имеет</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="72" t="inlineStr">
+        <is>
+          <t>Auszahlungsbetrag</t>
+        </is>
+      </c>
+      <c r="C19" s="73" t="n"/>
+      <c r="D19" s="73" t="n"/>
+      <c r="E19" s="73" t="n"/>
+      <c r="F19" s="68" t="n">
+        <v>3612.3</v>
+      </c>
+      <c r="G19" s="73" t="n"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Переведено на Sparkasse Hannover</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>АВГУСТ — СХОДЯТСЯ ЛИ ЧАСЫ С ГРАФИКОМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Строка расчётки</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>Часы</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>Ставка</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>В расчётке</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="64" t="inlineStr">
+        <is>
+          <t>Смен по графику (лист Dienstplan)</t>
+        </is>
+      </c>
+      <c r="C23" s="73" t="n"/>
+      <c r="D23" s="73" t="n"/>
+      <c r="E23" s="73" t="n"/>
+      <c r="F23" s="75">
+        <f>Dienstplan!$L$36</f>
+        <v/>
+      </c>
+      <c r="G23" s="73" t="n"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>16 ND + 2 TD = 18 смен × 12 ч</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="64" t="inlineStr">
+        <is>
+          <t>Оплачено по расчётке</t>
+        </is>
+      </c>
+      <c r="C24" s="73" t="n"/>
+      <c r="D24" s="73" t="n"/>
+      <c r="E24" s="73" t="n"/>
+      <c r="F24" s="75" t="n">
+        <v>216</v>
+      </c>
+      <c r="G24" s="73" t="n"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>168 (норма) + 48 (переработка)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="72" t="inlineStr">
+        <is>
+          <t>Разница</t>
+        </is>
+      </c>
+      <c r="C25" s="73" t="n"/>
+      <c r="D25" s="73" t="n"/>
+      <c r="E25" s="73" t="n"/>
+      <c r="F25" s="76">
+        <f>$F$23-$F$24</f>
+        <v/>
+      </c>
+      <c r="G25" s="73" t="n"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>0 = всё оплачено</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="64" t="inlineStr">
+        <is>
+          <t>Ночных часов по графику</t>
+        </is>
+      </c>
+      <c r="C26" s="73" t="n"/>
+      <c r="D26" s="73" t="n"/>
+      <c r="E26" s="73" t="n"/>
+      <c r="F26" s="75">
+        <f>Dienstplan!$AM$36</f>
+        <v/>
+      </c>
+      <c r="G26" s="73" t="n"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>20:00–06:00 БЕЗ тех, что попали на воскресенье — их работодатель платит как воскресные (50 %), а не как ночные (25 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="64" t="inlineStr">
+        <is>
+          <t>из них пришлось на воскресенье</t>
+        </is>
+      </c>
+      <c r="C27" s="73" t="n"/>
+      <c r="D27" s="73" t="n"/>
+      <c r="E27" s="73" t="n"/>
+      <c r="F27" s="75">
+        <f>Dienstplan!$M$36-Dienstplan!$AM$36</f>
+        <v/>
+      </c>
+      <c r="G27" s="73" t="n"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Всего ночных часов по графику 160. Совпадение надбавок: платится только самая высокая — § 3 Abs. 2 договора</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="64" t="inlineStr">
+        <is>
+          <t>Ночных по расчётке</t>
+        </is>
+      </c>
+      <c r="C28" s="73" t="n"/>
+      <c r="D28" s="73" t="n"/>
+      <c r="E28" s="73" t="n"/>
+      <c r="F28" s="75" t="n">
+        <v>132</v>
+      </c>
+      <c r="G28" s="73" t="n"/>
+      <c r="H28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="64" t="inlineStr">
+        <is>
+          <t>Воскресных по графику</t>
+        </is>
+      </c>
+      <c r="C29" s="73" t="n"/>
+      <c r="D29" s="73" t="n"/>
+      <c r="E29" s="73" t="n"/>
+      <c r="F29" s="75">
+        <f>Dienstplan!$N$36</f>
+        <v/>
+      </c>
+      <c r="G29" s="73" t="n"/>
+      <c r="H29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="64" t="inlineStr">
+        <is>
+          <t>Воскресных по расчётке</t>
+        </is>
+      </c>
+      <c r="C30" s="73" t="n"/>
+      <c r="D30" s="73" t="n"/>
+      <c r="E30" s="73" t="n"/>
+      <c r="F30" s="75" t="n">
+        <v>44</v>
+      </c>
+      <c r="G30" s="73" t="n"/>
+      <c r="H30" s="8" t="inlineStr"/>
+    </row>
+    <row r="32" ht="39" customHeight="1">
+      <c r="B32" s="77" t="inlineStr">
+        <is>
+          <t>Изначально в графике стояли смены 19.08 и 20.08 (TD) и 31.08 (ND) — получалось 240 ч и не хватало 24 ч. После проверки: 19.08, 20.08 и 31.08 были выходными. 18 смен × 12 ч = 216 ч — ровно столько и оплачено. Недоплаты за август НЕТ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Ночные 132 ч и воскресные 44 ч сошлись с графиком копейка в копейку — это подтверждает и время смен (ND 20:00–08:00, TD 08:00–20:00), и то, что перерыв из оплаты не вычитают.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="52" customHeight="1">
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Работодатель заплатил ЩЕДРЕЕ, чем написано в договоре: § 2 Abs. 3 разрешает не платить первые 8 ч переработки в месяц, но в расчётке оплачены все 216 ч (168 + 48), а не 208. Это +216,00 € брутто в твою пользу. Лист «Расчёт» считает строго по договору, поэтому там брутто 7.101 €, а в расчётке 7.317 €. Если хочешь, чтобы файл повторял расчётку точь-в-точь, поставь в «Настройках» «Переработка включена в оклад» = 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Почему ночных 132, а не 160: 16 ночных смен × 10 ч = 160 ночных часов, но 28 из них выпали на воскресенье. За них платят воскресные 50 %, а не ночные 25 % — надбавки не складываются. 160 − 28 = 132.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>ИЮЛЬ 2026 — Abrechnung vom 12.08.2026 (Eintritt 15.07.2026, 17 дней)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>Строка расчётки</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>Часы</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>Ставка</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>В расчётке</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="64" t="inlineStr">
+        <is>
+          <t>101 Stundenlohn</t>
+        </is>
+      </c>
+      <c r="C39" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="D39" s="69" t="n">
+        <v>26</v>
+      </c>
+      <c r="E39" s="29" t="inlineStr"/>
+      <c r="F39" s="69" t="n">
+        <v>1196</v>
+      </c>
+      <c r="G39" s="70">
+        <f>ROUND($C39*$D39*IF($E39="",1,$E39),2)</f>
+        <v/>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Ставка в июле была ещё 26,00 € (Teilzeit-Vertrag)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="64" t="inlineStr">
+        <is>
+          <t>103 Überstdgrundvergütung</t>
+        </is>
+      </c>
+      <c r="C40" s="32" t="n">
+        <v>74</v>
+      </c>
+      <c r="D40" s="69" t="n">
+        <v>26</v>
+      </c>
+      <c r="E40" s="29" t="inlineStr"/>
+      <c r="F40" s="69" t="n">
+        <v>1924</v>
+      </c>
+      <c r="G40" s="70">
+        <f>ROUND($C40*$D40*IF($E40="",1,$E40),2)</f>
+        <v/>
+      </c>
+      <c r="H40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="64" t="inlineStr">
+        <is>
+          <t>114 Nacht 25% frei</t>
+        </is>
+      </c>
+      <c r="C41" s="32" t="n">
+        <v>42</v>
+      </c>
+      <c r="D41" s="69" t="n">
+        <v>26</v>
+      </c>
+      <c r="E41" s="71" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F41" s="69" t="n">
+        <v>273</v>
+      </c>
+      <c r="G41" s="70">
+        <f>ROUND($C41*$D41*IF($E41="",1,$E41),2)</f>
+        <v/>
+      </c>
+      <c r="H41" s="8" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="64" t="inlineStr">
+        <is>
+          <t>115 Sonntag 50% frei</t>
+        </is>
+      </c>
+      <c r="C42" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="D42" s="69" t="n">
+        <v>26</v>
+      </c>
+      <c r="E42" s="71" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F42" s="69" t="n">
+        <v>260</v>
+      </c>
+      <c r="G42" s="70">
+        <f>ROUND($C42*$D42*IF($E42="",1,$E42),2)</f>
+        <v/>
+      </c>
+      <c r="H42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="72" t="inlineStr">
+        <is>
+          <t>Gesamt-Brutto</t>
+        </is>
+      </c>
+      <c r="C43" s="73" t="n"/>
+      <c r="D43" s="73" t="n"/>
+      <c r="E43" s="73" t="n"/>
+      <c r="F43" s="68" t="n">
+        <v>3653</v>
+      </c>
+      <c r="G43" s="74">
+        <f>SUM($F$39:$F$42)</f>
+        <v/>
+      </c>
+      <c r="H43" s="8" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="64" t="inlineStr">
+        <is>
+          <t>Lohnsteuer</t>
+        </is>
+      </c>
+      <c r="C44" s="73" t="n"/>
+      <c r="D44" s="73" t="n"/>
+      <c r="E44" s="73" t="n"/>
+      <c r="F44" s="69" t="n">
+        <v>-853.91</v>
+      </c>
+      <c r="G44" s="73" t="n"/>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>СТЕРИЛЬНО МНОГО: класс 6, потому что до 31.07 числился ещё и в KRH. Это законно, но переплату вернёт Steuererklärung за 2026 — примерно 800 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="64" t="inlineStr">
+        <is>
+          <t>Соцвзносы всего</t>
+        </is>
+      </c>
+      <c r="C45" s="73" t="n"/>
+      <c r="D45" s="73" t="n"/>
+      <c r="E45" s="73" t="n"/>
+      <c r="F45" s="69" t="n">
+        <v>-661.28</v>
+      </c>
+      <c r="G45" s="73" t="n"/>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>KV 274,40 + RV 290,16 + AV 40,56 + PV 56,16</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="72" t="inlineStr">
+        <is>
+          <t>Netto-Verdienst</t>
+        </is>
+      </c>
+      <c r="C46" s="73" t="n"/>
+      <c r="D46" s="73" t="n"/>
+      <c r="E46" s="73" t="n"/>
+      <c r="F46" s="68" t="n">
+        <v>2137.81</v>
+      </c>
+      <c r="G46" s="73" t="n"/>
+      <c r="H46" s="8" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="64" t="inlineStr">
+        <is>
+          <t>Abschlag / Vorschuss</t>
+        </is>
+      </c>
+      <c r="C47" s="73" t="n"/>
+      <c r="D47" s="73" t="n"/>
+      <c r="E47" s="73" t="n"/>
+      <c r="F47" s="69" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="G47" s="73" t="n"/>
+      <c r="H47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="72" t="inlineStr">
+        <is>
+          <t>Auszahlungsbetrag</t>
+        </is>
+      </c>
+      <c r="C48" s="73" t="n"/>
+      <c r="D48" s="73" t="n"/>
+      <c r="E48" s="73" t="n"/>
+      <c r="F48" s="68" t="n">
+        <v>137.81</v>
+      </c>
+      <c r="G48" s="73" t="n"/>
+      <c r="H48" s="8" t="inlineStr"/>
+    </row>
+    <row r="50" ht="19" customHeight="1">
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>ИЮЛЬ — ПЕРЕСЧЁТ (1. NB), проведён вместе с августом</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>Строка расчётки</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>Часы</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>Ставка</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>В расчётке</t>
+        </is>
+      </c>
+      <c r="G51" s="20" t="inlineStr">
+        <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="H51" s="20" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="64" t="inlineStr">
+        <is>
+          <t>N 114 Nacht 25% frei</t>
+        </is>
+      </c>
+      <c r="C52" s="32" t="n">
+        <v>18</v>
+      </c>
+      <c r="D52" s="69" t="n">
+        <v>26</v>
+      </c>
+      <c r="E52" s="71" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F52" s="69" t="n">
+        <v>117</v>
+      </c>
+      <c r="G52" s="70">
+        <f>ROUND($C52*$D52*IF($E52="",1,$E52),2)</f>
+        <v/>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>«N» = Nachberechnung, пересчёт задним числом. Нашли 18 неучтённых ночных часов</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="64" t="inlineStr">
+        <is>
+          <t>Новый Gesamt-Brutto июля</t>
+        </is>
+      </c>
+      <c r="C53" s="73" t="n"/>
+      <c r="D53" s="73" t="n"/>
+      <c r="E53" s="73" t="n"/>
+      <c r="F53" s="69" t="n">
+        <v>3770</v>
+      </c>
+      <c r="G53" s="73" t="n"/>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>3.653,00 + 117,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="64" t="inlineStr">
+        <is>
+          <t>Новый Netto июля</t>
+        </is>
+      </c>
+      <c r="C54" s="73" t="n"/>
+      <c r="D54" s="73" t="n"/>
+      <c r="E54" s="73" t="n"/>
+      <c r="F54" s="69" t="n">
+        <v>2254.81</v>
+      </c>
+      <c r="G54" s="73" t="n"/>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>2.137,81 + 117,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="64" t="inlineStr">
+        <is>
+          <t>Уже выплачено</t>
+        </is>
+      </c>
+      <c r="C55" s="73" t="n"/>
+      <c r="D55" s="73" t="n"/>
+      <c r="E55" s="73" t="n"/>
+      <c r="F55" s="69" t="n">
+        <v>-2137.81</v>
+      </c>
+      <c r="G55" s="73" t="n"/>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>2.000,00 аванс + 137,81 перевод</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="72" t="inlineStr">
+        <is>
+          <t>Доплата, проведённая в августе</t>
+        </is>
+      </c>
+      <c r="C56" s="73" t="n"/>
+      <c r="D56" s="73" t="n"/>
+      <c r="E56" s="73" t="n"/>
+      <c r="F56" s="68" t="n">
+        <v>117</v>
+      </c>
+      <c r="G56" s="73" t="n"/>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Та самая строка «aus NB 07/2026» в августовской расчётке</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="52" customHeight="1">
+      <c r="B58" s="78" t="inlineStr">
+        <is>
+          <t>ВАЖНО ПО ИЮЛЮ: пересчитали только НАДБАВКУ за ночь (18 ч × 26 € × 25 %). Сами 18 часов при этом в строку 101/103 не добавили — оплаченных часов как было 120, так и осталось. Если в июльском графике смен было больше, чем на 120 ч, — это надо предъявить. Срок по июлю: 3 месяца с 15.08.2026, то есть до 15.11.2026 (§ 14 Ausschlussfrist).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="19" customHeight="1">
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>ЧТО ВЫЯСНИЛОСЬ ПО ХОДУ</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>· Einspringzuschlag / Einspringprämie у работодателя НЕТ вообще — подтверждено письменно (Chris, 09/2026). В договоре её тоже нет. Поэтому в «Настройках» премия за Eingesprungen стоит 0,00 €.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>· Verpflegungszuschuss в расчётке отсутствует. Единственная добавка к нетто — 117,00 €, и это ночные за июль.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>· Строки Zeitkonto / Arbeitszeitkonto / Übertrag / Saldo в расчётке НЕТ ни одной. Счёт часов, если он ведётся, виден только в Zeitnachweis — его надо запрашивать отдельно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="26" customHeight="1">
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>· Arbeitszeitkonto был прописан в СТАРОМ Teilzeit-договоре (§ 4 Abs. 1). В новом Vollzeit-договоре с 01.08.2026 такого пункта НЕТ — значит формального основания складывать часы на счёт больше не существует.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>· Доп. взнос кассы AOK Baden-Württemberg = 2,99 % (не средние 2,9 %). В «Настройках» исправлено.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>· Доплата бездетным в Pflegeversicherung (0,6 %) не удерживается — ребёнок учтён правильно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>· Надбавки провели полностью свободными от взносов, хотя § 1 SvEV освобождает только с базы 25 €/ч. Сейчас это в твою пользу (~110 € в месяц), но уменьшает будущую пенсию на эту же базу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="26" customHeight="1">
+      <c r="B69" s="78" t="inlineStr">
+        <is>
+          <t>Сроки, которые нельзя пропустить: по июлю — до 15.11.2026, по августу — до 14.12.2026. Разговор в WhatsApp сроки НЕ прерывает, нужна письменная претензия (e-mail достаточно).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="B64:H64"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B63:H63"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="B50:H50"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B66:H66"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B60:H60"/>
+    <mergeCell ref="B67:H67"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="B34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2415,11 +3556,11 @@
         </is>
       </c>
       <c r="D53" s="15" t="n">
-        <v>0.029</v>
+        <v>0.0299</v>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>средний 2026 — 2,9 %. Поставь ставку СВОЕЙ кассы</t>
+          <t>AOK Baden-Württemberg 2026 = 2,99 % (проверено по Lohnabrechnung 08/2026: 511,21 € / 5.812,50 € = 8,795 % = (14,6 % + 2,99 %) / 2)</t>
         </is>
       </c>
     </row>
@@ -6425,19 +7566,11 @@
       </c>
       <c r="D23" s="30" t="inlineStr">
         <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="E23" s="30" t="inlineStr">
-        <is>
-          <t>Arbeit</t>
-        </is>
-      </c>
-      <c r="F23" s="30" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>FREI</t>
+        </is>
+      </c>
+      <c r="E23" s="30" t="inlineStr"/>
+      <c r="F23" s="30" t="inlineStr"/>
       <c r="G23" s="30" t="inlineStr"/>
       <c r="H23" s="31">
         <f>IF($D23="ND",Настройки!$D$42,IF($D23="TD",Настройки!$D$39,""))</f>
@@ -6587,19 +7720,11 @@
       </c>
       <c r="D24" s="30" t="inlineStr">
         <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="E24" s="30" t="inlineStr">
-        <is>
-          <t>Arbeit</t>
-        </is>
-      </c>
-      <c r="F24" s="30" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>FREI</t>
+        </is>
+      </c>
+      <c r="E24" s="30" t="inlineStr"/>
+      <c r="F24" s="30" t="inlineStr"/>
       <c r="G24" s="30" t="inlineStr"/>
       <c r="H24" s="31">
         <f>IF($D24="ND",Настройки!$D$42,IF($D24="TD",Настройки!$D$39,""))</f>
@@ -7069,7 +8194,11 @@
           <t>Arbeit</t>
         </is>
       </c>
-      <c r="F27" s="30" t="inlineStr"/>
+      <c r="F27" s="30" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G27" s="30" t="inlineStr"/>
       <c r="H27" s="31">
         <f>IF($D27="ND",Настройки!$D$42,IF($D27="TD",Настройки!$D$39,""))</f>
@@ -8325,14 +9454,10 @@
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="E35" s="30" t="inlineStr">
-        <is>
-          <t>Arbeit</t>
-        </is>
-      </c>
+          <t>FREI</t>
+        </is>
+      </c>
+      <c r="E35" s="30" t="inlineStr"/>
       <c r="F35" s="30" t="inlineStr"/>
       <c r="G35" s="30" t="inlineStr"/>
       <c r="H35" s="31">
@@ -8524,6 +9649,22 @@
       </c>
       <c r="T36" s="38" t="n"/>
       <c r="U36" s="38" t="n"/>
+      <c r="AJ36" s="41">
+        <f>SUM(AJ5:AJ35)</f>
+        <v/>
+      </c>
+      <c r="AK36" s="41">
+        <f>SUM(AK5:AK35)</f>
+        <v/>
+      </c>
+      <c r="AL36" s="41">
+        <f>SUM(AL5:AL35)</f>
+        <v/>
+      </c>
+      <c r="AM36" s="41">
+        <f>SUM(AM5:AM35)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8589,14 +9730,14 @@
       </c>
     </row>
     <row r="4" ht="19" customHeight="1">
-      <c r="B4" s="41" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>A. ЧАСЫ / ARBEITSZEIT</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>Отработано часов (факт)</t>
         </is>
@@ -8606,7 +9747,7 @@
           <t>Ist-Stunden</t>
         </is>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="44">
         <f>Dienstplan!L36</f>
         <v/>
       </c>
@@ -8617,7 +9758,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>Плановая норма месяца</t>
         </is>
@@ -8627,7 +9768,7 @@
           <t>Sollstunden</t>
         </is>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="44">
         <f>ROUND(Настройки!$D$12*Настройки!$D$20,2)</f>
         <v/>
       </c>
@@ -8638,7 +9779,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="42" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>Разница за месяц</t>
         </is>
@@ -8648,7 +9789,7 @@
           <t>Differenz</t>
         </is>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="44">
         <f>D5-D6</f>
         <v/>
       </c>
@@ -8659,7 +9800,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="42" t="inlineStr">
+      <c r="B8" s="43" t="inlineStr">
         <is>
           <t>Ночных часов</t>
         </is>
@@ -8669,7 +9810,7 @@
           <t>Nachtstunden</t>
         </is>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="44">
         <f>Dienstplan!M36</f>
         <v/>
       </c>
@@ -8680,7 +9821,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="42" t="inlineStr">
+      <c r="B9" s="43" t="inlineStr">
         <is>
           <t>Воскресных часов</t>
         </is>
@@ -8690,14 +9831,14 @@
           <t>Sonntagsstunden</t>
         </is>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="44">
         <f>Dienstplan!N36</f>
         <v/>
       </c>
       <c r="E9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" s="42" t="inlineStr">
+      <c r="B10" s="43" t="inlineStr">
         <is>
           <t>Праздничных часов</t>
         </is>
@@ -8707,14 +9848,14 @@
           <t>Feiertagsstunden</t>
         </is>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="44">
         <f>Dienstplan!O36</f>
         <v/>
       </c>
       <c r="E10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="B11" s="42" t="inlineStr">
+      <c r="B11" s="43" t="inlineStr">
         <is>
           <t>Смен «Eingesprungen»</t>
         </is>
@@ -8724,24 +9865,24 @@
           <t>Einspringdienste</t>
         </is>
       </c>
-      <c r="D11" s="44">
+      <c r="D11" s="45">
         <f>Dienstplan!F36</f>
         <v/>
       </c>
       <c r="E11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="B12" s="45" t="n"/>
+      <c r="B12" s="46" t="n"/>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="B13" s="41" t="inlineStr">
+      <c r="B13" s="42" t="inlineStr">
         <is>
           <t>B. СЧЁТ ЧАСОВ / ARBEITSZEITKONTO</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="42" t="inlineStr">
+      <c r="B14" s="43" t="inlineStr">
         <is>
           <t>Перенос из прошлого месяца</t>
         </is>
@@ -8751,7 +9892,7 @@
           <t>Übertrag aus Vormonat</t>
         </is>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="44">
         <f>Настройки!$D$18</f>
         <v/>
       </c>
@@ -8762,7 +9903,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="42" t="inlineStr">
+      <c r="B15" s="43" t="inlineStr">
         <is>
           <t>Счёт часов до выплаты</t>
         </is>
@@ -8772,14 +9913,14 @@
           <t>Stundenkonto vor Auszahlung</t>
         </is>
       </c>
-      <c r="D15" s="43">
+      <c r="D15" s="44">
         <f>D14+D7</f>
         <v/>
       </c>
       <c r="E15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="B16" s="42" t="inlineStr">
+      <c r="B16" s="43" t="inlineStr">
         <is>
           <t>Пропадает: включено в оклад</t>
         </is>
@@ -8789,7 +9930,7 @@
           <t>pauschal abgegolten (§ 2 Abs. 3)</t>
         </is>
       </c>
-      <c r="D16" s="43">
+      <c r="D16" s="44">
         <f>MIN(MAX(0,D7),Настройки!$D$14)</f>
         <v/>
       </c>
@@ -8800,7 +9941,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="42" t="inlineStr">
+      <c r="B17" s="43" t="inlineStr">
         <is>
           <t>Доступно к оплате</t>
         </is>
@@ -8810,7 +9951,7 @@
           <t>auszahlbar</t>
         </is>
       </c>
-      <c r="D17" s="43">
+      <c r="D17" s="44">
         <f>MAX(0,D15-D16)</f>
         <v/>
       </c>
@@ -8821,7 +9962,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="42" t="inlineStr">
+      <c r="B18" s="43" t="inlineStr">
         <is>
           <t>Оплачено в этом месяце</t>
         </is>
@@ -8831,7 +9972,7 @@
           <t>ausgezahlte Überstunden</t>
         </is>
       </c>
-      <c r="D18" s="43">
+      <c r="D18" s="44">
         <f>IF(Настройки!$D$16="ja",MAX(0,MIN(D17,Настройки!$D$15)),0)</f>
         <v/>
       </c>
@@ -8842,7 +9983,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="42" t="inlineStr">
+      <c r="B19" s="43" t="inlineStr">
         <is>
           <t>ПЕРЕНОС НА СЛЕДУЮЩИЙ МЕСЯЦ</t>
         </is>
@@ -8852,7 +9993,7 @@
           <t>Übertrag in den Folgemonat</t>
         </is>
       </c>
-      <c r="D19" s="46">
+      <c r="D19" s="47">
         <f>D15-D16-D18</f>
         <v/>
       </c>
@@ -8863,7 +10004,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="42" t="inlineStr">
+      <c r="B20" s="43" t="inlineStr">
         <is>
           <t>Стоимость непогашенных часов</t>
         </is>
@@ -8873,7 +10014,7 @@
           <t>Wert des Stundenkontos</t>
         </is>
       </c>
-      <c r="D20" s="47">
+      <c r="D20" s="48">
         <f>ROUND(D19*Настройки!$D$10,2)</f>
         <v/>
       </c>
@@ -8884,7 +10025,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="42" t="inlineStr">
+      <c r="B21" s="43" t="inlineStr">
         <is>
           <t>Оплачено бы БЕЗ лимита 60 ч</t>
         </is>
@@ -8894,7 +10035,7 @@
           <t>ohne 60-Stunden-Deckel</t>
         </is>
       </c>
-      <c r="D21" s="48">
+      <c r="D21" s="49">
         <f>ROUND(D17*Настройки!$D$10,2)</f>
         <v/>
       </c>
@@ -8905,17 +10046,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="45" t="n"/>
+      <c r="B22" s="46" t="n"/>
     </row>
     <row r="23" ht="19" customHeight="1">
-      <c r="B23" s="41" t="inlineStr">
+      <c r="B23" s="42" t="inlineStr">
         <is>
           <t>C. БРУТТО / BRUTTOENTGELT</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="42" t="inlineStr">
+      <c r="B24" s="43" t="inlineStr">
         <is>
           <t>Оклад</t>
         </is>
@@ -8925,7 +10066,7 @@
           <t>Grundvergütung § 3 Abs. 1</t>
         </is>
       </c>
-      <c r="D24" s="48">
+      <c r="D24" s="49">
         <f>ROUND(Настройки!$D$11*Настройки!$D$20,2)</f>
         <v/>
       </c>
@@ -8936,7 +10077,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="42" t="inlineStr">
+      <c r="B25" s="43" t="inlineStr">
         <is>
           <t>Оплата переработки</t>
         </is>
@@ -8946,7 +10087,7 @@
           <t>Überstundenvergütung</t>
         </is>
       </c>
-      <c r="D25" s="48">
+      <c r="D25" s="49">
         <f>ROUND(D18*Настройки!$D$10*(1+Настройки!$D$17),2)</f>
         <v/>
       </c>
@@ -8957,7 +10098,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="42" t="inlineStr">
+      <c r="B26" s="43" t="inlineStr">
         <is>
           <t>Надбавки всего</t>
         </is>
@@ -8967,7 +10108,7 @@
           <t>Zeitzuschläge gesamt</t>
         </is>
       </c>
-      <c r="D26" s="48">
+      <c r="D26" s="49">
         <f>Dienstplan!Q36</f>
         <v/>
       </c>
@@ -8978,7 +10119,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="42" t="inlineStr">
+      <c r="B27" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">   из них без подоходного налога</t>
         </is>
@@ -8988,14 +10129,14 @@
           <t xml:space="preserve">   steuerfrei § 3b EStG</t>
         </is>
       </c>
-      <c r="D27" s="48">
+      <c r="D27" s="49">
         <f>Dienstplan!R36</f>
         <v/>
       </c>
       <c r="E27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="B28" s="42" t="inlineStr">
+      <c r="B28" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">   из них без соцвзносов</t>
         </is>
@@ -9005,7 +10146,7 @@
           <t xml:space="preserve">   SV-frei § 1 SvEV</t>
         </is>
       </c>
-      <c r="D28" s="48">
+      <c r="D28" s="49">
         <f>Dienstplan!S36</f>
         <v/>
       </c>
@@ -9016,7 +10157,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="42" t="inlineStr">
+      <c r="B29" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">   облагается налогом</t>
         </is>
@@ -9026,14 +10167,14 @@
           <t xml:space="preserve">   steuerpflichtiger Anteil</t>
         </is>
       </c>
-      <c r="D29" s="48">
+      <c r="D29" s="49">
         <f>D26-D27</f>
         <v/>
       </c>
       <c r="E29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="B30" s="42" t="inlineStr">
+      <c r="B30" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">   облагается взносами</t>
         </is>
@@ -9043,14 +10184,14 @@
           <t xml:space="preserve">   SV-pflichtiger Anteil</t>
         </is>
       </c>
-      <c r="D30" s="48">
+      <c r="D30" s="49">
         <f>D26-D28</f>
         <v/>
       </c>
       <c r="E30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="B31" s="42" t="inlineStr">
+      <c r="B31" s="43" t="inlineStr">
         <is>
           <t>Премии за Eingesprungen</t>
         </is>
@@ -9060,7 +10201,7 @@
           <t>Einspringprämien</t>
         </is>
       </c>
-      <c r="D31" s="48">
+      <c r="D31" s="49">
         <f>ROUND(D11*Настройки!$D$19,2)</f>
         <v/>
       </c>
@@ -9071,7 +10212,7 @@
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="49" t="inlineStr">
+      <c r="B32" s="50" t="inlineStr">
         <is>
           <t>БРУТТО ВСЕГО</t>
         </is>
@@ -9081,14 +10222,14 @@
           <t>GESAMTBRUTTO</t>
         </is>
       </c>
-      <c r="D32" s="50">
+      <c r="D32" s="51">
         <f>D24+D25+D26+D31</f>
         <v/>
       </c>
       <c r="E32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="B33" s="42" t="inlineStr">
+      <c r="B33" s="43" t="inlineStr">
         <is>
           <t>Налогооблагаемое брутто</t>
         </is>
@@ -9098,7 +10239,7 @@
           <t>steuerpflichtiges Brutto</t>
         </is>
       </c>
-      <c r="D33" s="48">
+      <c r="D33" s="49">
         <f>D24+D25+D31+D29</f>
         <v/>
       </c>
@@ -9109,7 +10250,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="42" t="inlineStr">
+      <c r="B34" s="43" t="inlineStr">
         <is>
           <t>База для соцвзносов</t>
         </is>
@@ -9119,7 +10260,7 @@
           <t>SV-Brutto</t>
         </is>
       </c>
-      <c r="D34" s="48">
+      <c r="D34" s="49">
         <f>D24+D25+D31+D30</f>
         <v/>
       </c>
@@ -9130,17 +10271,17 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="45" t="n"/>
+      <c r="B35" s="46" t="n"/>
     </row>
     <row r="36" ht="19" customHeight="1">
-      <c r="B36" s="41" t="inlineStr">
+      <c r="B36" s="42" t="inlineStr">
         <is>
           <t>D. СОЦВЗНОСЫ (доля работника)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="42" t="inlineStr">
+      <c r="B37" s="43" t="inlineStr">
         <is>
           <t>Медицинское страхование</t>
         </is>
@@ -9150,7 +10291,7 @@
           <t>Krankenversicherung</t>
         </is>
       </c>
-      <c r="D37" s="48">
+      <c r="D37" s="49">
         <f>ROUND(MIN(D34,Настройки!$D$58)*(Настройки!$D$52/2+Настройки!$D$53/2),2)</f>
         <v/>
       </c>
@@ -9161,7 +10302,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="42" t="inlineStr">
+      <c r="B38" s="43" t="inlineStr">
         <is>
           <t>Страхование по уходу</t>
         </is>
@@ -9171,7 +10312,7 @@
           <t>Pflegeversicherung</t>
         </is>
       </c>
-      <c r="D38" s="48">
+      <c r="D38" s="49">
         <f>ROUND(MIN(D34,Настройки!$D$58)*(Настройки!$D$54/2+IF(Настройки!$D$51="ja",Настройки!$D$55,0)),2)</f>
         <v/>
       </c>
@@ -9182,7 +10323,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="42" t="inlineStr">
+      <c r="B39" s="43" t="inlineStr">
         <is>
           <t>Пенсионное страхование</t>
         </is>
@@ -9192,7 +10333,7 @@
           <t>Rentenversicherung</t>
         </is>
       </c>
-      <c r="D39" s="48">
+      <c r="D39" s="49">
         <f>ROUND(MIN(D34,Настройки!$D$59)*Настройки!$D$56/2,2)</f>
         <v/>
       </c>
@@ -9203,7 +10344,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="42" t="inlineStr">
+      <c r="B40" s="43" t="inlineStr">
         <is>
           <t>Страхование по безработице</t>
         </is>
@@ -9213,7 +10354,7 @@
           <t>Arbeitslosenversicherung</t>
         </is>
       </c>
-      <c r="D40" s="48">
+      <c r="D40" s="49">
         <f>ROUND(MIN(D34,Настройки!$D$59)*Настройки!$D$57/2,2)</f>
         <v/>
       </c>
@@ -9224,7 +10365,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="42" t="inlineStr">
+      <c r="B41" s="43" t="inlineStr">
         <is>
           <t>СОЦВЗНОСЫ ВСЕГО</t>
         </is>
@@ -9234,24 +10375,24 @@
           <t>SV gesamt</t>
         </is>
       </c>
-      <c r="D41" s="48">
+      <c r="D41" s="49">
         <f>D37+D38+D39+D40</f>
         <v/>
       </c>
       <c r="E41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="B42" s="45" t="n"/>
+      <c r="B42" s="46" t="n"/>
     </row>
     <row r="43" ht="19" customHeight="1">
-      <c r="B43" s="41" t="inlineStr">
+      <c r="B43" s="42" t="inlineStr">
         <is>
           <t>E. НАЛОГИ</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="42" t="inlineStr">
+      <c r="B44" s="43" t="inlineStr">
         <is>
           <t>Подоходный налог</t>
         </is>
@@ -9261,7 +10402,7 @@
           <t>Lohnsteuer</t>
         </is>
       </c>
-      <c r="D44" s="48">
+      <c r="D44" s="49">
         <f>Lohnsteuer!D26</f>
         <v/>
       </c>
@@ -9272,7 +10413,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="42" t="inlineStr">
+      <c r="B45" s="43" t="inlineStr">
         <is>
           <t>Надбавка солидарности</t>
         </is>
@@ -9282,7 +10423,7 @@
           <t>Solidaritätszuschlag</t>
         </is>
       </c>
-      <c r="D45" s="48">
+      <c r="D45" s="49">
         <f>Lohnsteuer!D31</f>
         <v/>
       </c>
@@ -9293,7 +10434,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="42" t="inlineStr">
+      <c r="B46" s="43" t="inlineStr">
         <is>
           <t>Церковный налог</t>
         </is>
@@ -9303,14 +10444,14 @@
           <t>Kirchensteuer</t>
         </is>
       </c>
-      <c r="D46" s="48">
+      <c r="D46" s="49">
         <f>Lohnsteuer!D32</f>
         <v/>
       </c>
       <c r="E46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="B47" s="42" t="inlineStr">
+      <c r="B47" s="43" t="inlineStr">
         <is>
           <t>НАЛОГИ ВСЕГО</t>
         </is>
@@ -9320,24 +10461,24 @@
           <t>Steuern gesamt</t>
         </is>
       </c>
-      <c r="D47" s="48">
+      <c r="D47" s="49">
         <f>D44+D45+D46</f>
         <v/>
       </c>
       <c r="E47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="B48" s="45" t="n"/>
+      <c r="B48" s="46" t="n"/>
     </row>
     <row r="49" ht="19" customHeight="1">
-      <c r="B49" s="41" t="inlineStr">
+      <c r="B49" s="42" t="inlineStr">
         <is>
           <t>F. НА РУКИ</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
-      <c r="B50" s="49" t="inlineStr">
+      <c r="B50" s="50" t="inlineStr">
         <is>
           <t>НЕТТО (на счёт)</t>
         </is>
@@ -9347,7 +10488,7 @@
           <t>NETTOVERDIENST</t>
         </is>
       </c>
-      <c r="D50" s="50">
+      <c r="D50" s="51">
         <f>D32-D41-D47</f>
         <v/>
       </c>
@@ -9358,7 +10499,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="42" t="inlineStr">
+      <c r="B51" s="43" t="inlineStr">
         <is>
           <t>Нетто за час фактической работы</t>
         </is>
@@ -9368,14 +10509,14 @@
           <t>Nettostundenlohn</t>
         </is>
       </c>
-      <c r="D51" s="48">
+      <c r="D51" s="49">
         <f>IF(D5=0,0,ROUND(D50/D5,2))</f>
         <v/>
       </c>
       <c r="E51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="B52" s="42" t="inlineStr">
+      <c r="B52" s="43" t="inlineStr">
         <is>
           <t>Доля отчислений</t>
         </is>
@@ -9385,24 +10526,24 @@
           <t>Abzugsquote</t>
         </is>
       </c>
-      <c r="D52" s="51">
+      <c r="D52" s="52">
         <f>IF(D32=0,0,(D41+D47)/D32)</f>
         <v/>
       </c>
       <c r="E52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="B53" s="45" t="n"/>
+      <c r="B53" s="46" t="n"/>
     </row>
     <row r="54" ht="19" customHeight="1">
-      <c r="B54" s="41" t="inlineStr">
+      <c r="B54" s="42" t="inlineStr">
         <is>
           <t>G. СПРАВОЧНО: расходы работодателя</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="42" t="inlineStr">
+      <c r="B55" s="43" t="inlineStr">
         <is>
           <t>KV работодатель</t>
         </is>
@@ -9412,14 +10553,14 @@
           <t>AG-Anteil KV</t>
         </is>
       </c>
-      <c r="D55" s="48">
+      <c r="D55" s="49">
         <f>ROUND(MIN(D34,Настройки!$D$58)*(Настройки!$D$52/2+Настройки!$D$53/2),2)</f>
         <v/>
       </c>
       <c r="E55" s="8" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="B56" s="42" t="inlineStr">
+      <c r="B56" s="43" t="inlineStr">
         <is>
           <t>PV работодатель</t>
         </is>
@@ -9429,14 +10570,14 @@
           <t>AG-Anteil PV</t>
         </is>
       </c>
-      <c r="D56" s="48">
+      <c r="D56" s="49">
         <f>ROUND(MIN(D34,Настройки!$D$58)*Настройки!$D$54/2,2)</f>
         <v/>
       </c>
       <c r="E56" s="8" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="B57" s="42" t="inlineStr">
+      <c r="B57" s="43" t="inlineStr">
         <is>
           <t>RV работодатель</t>
         </is>
@@ -9446,14 +10587,14 @@
           <t>AG-Anteil RV</t>
         </is>
       </c>
-      <c r="D57" s="48">
+      <c r="D57" s="49">
         <f>ROUND(MIN(D34,Настройки!$D$59)*Настройки!$D$56/2,2)</f>
         <v/>
       </c>
       <c r="E57" s="8" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="B58" s="42" t="inlineStr">
+      <c r="B58" s="43" t="inlineStr">
         <is>
           <t>AV работодатель</t>
         </is>
@@ -9463,14 +10604,14 @@
           <t>AG-Anteil AV</t>
         </is>
       </c>
-      <c r="D58" s="48">
+      <c r="D58" s="49">
         <f>ROUND(MIN(D34,Настройки!$D$59)*Настройки!$D$57/2,2)</f>
         <v/>
       </c>
       <c r="E58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="B59" s="42" t="inlineStr">
+      <c r="B59" s="43" t="inlineStr">
         <is>
           <t>Всего расходы работодателя</t>
         </is>
@@ -9480,7 +10621,7 @@
           <t>Gesamtkosten Arbeitgeber</t>
         </is>
       </c>
-      <c r="D59" s="48">
+      <c r="D59" s="49">
         <f>D32+D55+D56+D57+D58</f>
         <v/>
       </c>
@@ -9491,17 +10632,17 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="45" t="n"/>
+      <c r="B60" s="46" t="n"/>
     </row>
     <row r="61" ht="19" customHeight="1">
-      <c r="B61" s="41" t="inlineStr">
+      <c r="B61" s="42" t="inlineStr">
         <is>
           <t>H. ПРОВЕРКА ПО ЗАКОНУ</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="42" t="inlineStr">
+      <c r="B62" s="43" t="inlineStr">
         <is>
           <t>Ср. часов в неделю</t>
         </is>
@@ -9511,7 +10652,7 @@
           <t>Ø Wochenarbeitszeit</t>
         </is>
       </c>
-      <c r="D62" s="43">
+      <c r="D62" s="44">
         <f>ROUND(D5/(Настройки!$D$6/7),2)</f>
         <v/>
       </c>
@@ -9522,7 +10663,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="42" t="inlineStr">
+      <c r="B63" s="43" t="inlineStr">
         <is>
           <t>Смен длиннее 10 ч</t>
         </is>
@@ -9532,7 +10673,7 @@
           <t>Dienste &gt; 10 h</t>
         </is>
       </c>
-      <c r="D63" s="44">
+      <c r="D63" s="45">
         <f>COUNTIF(Dienstplan!L5:L35,"&gt;10")</f>
         <v/>
       </c>
@@ -9543,7 +10684,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="42" t="inlineStr">
+      <c r="B64" s="43" t="inlineStr">
         <is>
           <t>Ночных смен длиннее 8 ч</t>
         </is>
@@ -9553,7 +10694,7 @@
           <t>Nachtdienste &gt; 8 h</t>
         </is>
       </c>
-      <c r="D64" s="44">
+      <c r="D64" s="45">
         <f>COUNTIFS(Dienstplan!D5:D35,"ND",Dienstplan!L5:L35,"&gt;8")</f>
         <v/>
       </c>
@@ -9564,7 +10705,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="42" t="inlineStr">
+      <c r="B65" s="43" t="inlineStr">
         <is>
           <t>Нарушений отдыха 11 ч</t>
         </is>
@@ -9574,7 +10715,7 @@
           <t>Ruhezeit &lt; 11 h</t>
         </is>
       </c>
-      <c r="D65" s="44">
+      <c r="D65" s="45">
         <f>COUNTIFS(Dienstplan!T5:T35,"&lt;11",Dienstplan!T5:T35,"&gt;0")</f>
         <v/>
       </c>
@@ -9585,7 +10726,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="42" t="inlineStr">
+      <c r="B66" s="43" t="inlineStr">
         <is>
           <t>Смен, задевающих воскресенье</t>
         </is>
@@ -9595,7 +10736,7 @@
           <t>Sonntagsarbeit</t>
         </is>
       </c>
-      <c r="D66" s="44">
+      <c r="D66" s="45">
         <f>COUNTIF(Dienstplan!N5:N35,"&gt;0")</f>
         <v/>
       </c>
@@ -9606,7 +10747,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="42" t="inlineStr">
+      <c r="B67" s="43" t="inlineStr">
         <is>
           <t>Ставка ≥ Pflegemindestlohn?</t>
         </is>
@@ -9616,7 +10757,7 @@
           <t>Pflegemindestlohn 21,03 €</t>
         </is>
       </c>
-      <c r="D67" s="52">
+      <c r="D67" s="53">
         <f>IF(Настройки!$D$10&gt;=21.03,"да / ja","НЕТ — проверить!")</f>
         <v/>
       </c>
@@ -9709,7 +10850,7 @@
           <t>steuerpflichtiger Monatslohn</t>
         </is>
       </c>
-      <c r="D5" s="48">
+      <c r="D5" s="49">
         <f>Расчёт!D33</f>
         <v/>
       </c>
@@ -9738,7 +10879,7 @@
           <t>hochgerechneter Jahresarbeitslohn</t>
         </is>
       </c>
-      <c r="D6" s="48">
+      <c r="D6" s="49">
         <f>ROUND(D5*12,2)</f>
         <v/>
       </c>
@@ -9767,7 +10908,7 @@
           <t>Steuerklasse</t>
         </is>
       </c>
-      <c r="D7" s="44">
+      <c r="D7" s="45">
         <f>Настройки!$D$47</f>
         <v/>
       </c>
@@ -9817,7 +10958,7 @@
           <t>Arbeitnehmer-Pauschbetrag</t>
         </is>
       </c>
-      <c r="D10" s="48">
+      <c r="D10" s="49">
         <f>IF(Настройки!$D$47&lt;6,Настройки!$D$62,0)</f>
         <v/>
       </c>
@@ -9846,7 +10987,7 @@
           <t>Sonderausgaben-Pauschbetrag</t>
         </is>
       </c>
-      <c r="D11" s="48">
+      <c r="D11" s="49">
         <f>IF(Настройки!$D$47&lt;6,Настройки!$D$63,0)</f>
         <v/>
       </c>
@@ -9875,7 +11016,7 @@
           <t>Entlastungsbetrag Alleinerziehende</t>
         </is>
       </c>
-      <c r="D12" s="48">
+      <c r="D12" s="49">
         <f>IF(Настройки!$D$47=2,Настройки!$D$64,0)</f>
         <v/>
       </c>
@@ -9911,7 +11052,7 @@
           <t>Teilbetrag Rentenversicherung</t>
         </is>
       </c>
-      <c r="D15" s="48">
+      <c r="D15" s="49">
         <f>ROUND(MIN(D6,Настройки!$D$59*12)*Настройки!$D$56/2,2)</f>
         <v/>
       </c>
@@ -9932,7 +11073,7 @@
           <t>Teilbetrag Krankenversicherung</t>
         </is>
       </c>
-      <c r="D16" s="48">
+      <c r="D16" s="49">
         <f>ROUND(MIN(D6,Настройки!$D$58*12)*(Настройки!$D$52/2+Настройки!$D$53/2),2)</f>
         <v/>
       </c>
@@ -9949,7 +11090,7 @@
           <t>Teilbetrag Pflegeversicherung</t>
         </is>
       </c>
-      <c r="D17" s="48">
+      <c r="D17" s="49">
         <f>ROUND(MIN(D6,Настройки!$D$58*12)*(Настройки!$D$54/2+IF(Настройки!$D$51="ja",Настройки!$D$55,0)),2)</f>
         <v/>
       </c>
@@ -9966,7 +11107,7 @@
           <t>Teilbetrag Arbeitslosenversicherung</t>
         </is>
       </c>
-      <c r="D18" s="48">
+      <c r="D18" s="49">
         <f>IF(Настройки!$D$65="ja",ROUND(MIN(MIN(D6,Настройки!$D$59*12)*Настройки!$D$57/2,MAX(0,1900-D16-D17)),2),0)</f>
         <v/>
       </c>
@@ -9987,7 +11128,7 @@
           <t>Vorsorgepauschale gesamt</t>
         </is>
       </c>
-      <c r="D19" s="48">
+      <c r="D19" s="49">
         <f>D15+D16+D17+D18</f>
         <v/>
       </c>
@@ -10011,7 +11152,7 @@
           <t>zu versteuerndes Einkommen (zvE)</t>
         </is>
       </c>
-      <c r="D22" s="48">
+      <c r="D22" s="49">
         <f>MAX(0,ROUNDDOWN(D6-D10-D11-D12-D19,0))</f>
         <v/>
       </c>
@@ -10032,7 +11173,7 @@
           <t>Grundtarif § 32a Abs. 1</t>
         </is>
       </c>
-      <c r="D23" s="48">
+      <c r="D23" s="49">
         <f>IF(D22&lt;=Настройки!$D$67,0,IF(D22&lt;=Настройки!$D$68,ROUNDDOWN(($G$4*((D22-Настройки!$D$67)/10000)+$G$5)*((D22-Настройки!$D$67)/10000),0),IF(D22&lt;=Настройки!$D$69,ROUNDDOWN(($G$6*((D22-Настройки!$D$68)/10000)+$G$7)*((D22-Настройки!$D$68)/10000)+$G$8,0),IF(D22&lt;=Настройки!$D$70,ROUNDDOWN($G$9*D22-$G$10,0),ROUNDDOWN($G$11*D22-$G$12,0)))))</f>
         <v/>
       </c>
@@ -10053,7 +11194,7 @@
           <t>Splittingtarif § 32a Abs. 5</t>
         </is>
       </c>
-      <c r="D24" s="48">
+      <c r="D24" s="49">
         <f>2*(IF(ROUNDDOWN(D22/2,0)&lt;=Настройки!$D$67,0,IF(ROUNDDOWN(D22/2,0)&lt;=Настройки!$D$68,ROUNDDOWN(($G$4*((ROUNDDOWN(D22/2,0)-Настройки!$D$67)/10000)+$G$5)*((ROUNDDOWN(D22/2,0)-Настройки!$D$67)/10000),0),IF(ROUNDDOWN(D22/2,0)&lt;=Настройки!$D$69,ROUNDDOWN(($G$6*((ROUNDDOWN(D22/2,0)-Настройки!$D$68)/10000)+$G$7)*((ROUNDDOWN(D22/2,0)-Настройки!$D$68)/10000)+$G$8,0),IF(ROUNDDOWN(D22/2,0)&lt;=Настройки!$D$70,ROUNDDOWN($G$9*ROUNDDOWN(D22/2,0)-$G$10,0),ROUNDDOWN($G$11*ROUNDDOWN(D22/2,0)-$G$12,0))))))</f>
         <v/>
       </c>
@@ -10074,14 +11215,14 @@
           <t>Jahreslohnsteuer</t>
         </is>
       </c>
-      <c r="D25" s="48">
+      <c r="D25" s="49">
         <f>IF(Настройки!$D$47=3,D24,D23)</f>
         <v/>
       </c>
       <c r="E25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="B26" s="53" t="inlineStr">
+      <c r="B26" s="54" t="inlineStr">
         <is>
           <t>ПОДОХОДНЫЙ НАЛОГ ЗА МЕСЯЦ</t>
         </is>
@@ -10091,7 +11232,7 @@
           <t>Lohnsteuer monatlich</t>
         </is>
       </c>
-      <c r="D26" s="50">
+      <c r="D26" s="51">
         <f>ROUND(D25/12,2)</f>
         <v/>
       </c>
@@ -10115,7 +11256,7 @@
           <t>Soli-Freigrenze</t>
         </is>
       </c>
-      <c r="D29" s="48">
+      <c r="D29" s="49">
         <f>IF(Настройки!$D$47=3,Настройки!$D$66*2,Настройки!$D$66)</f>
         <v/>
       </c>
@@ -10136,7 +11277,7 @@
           <t>Solidaritätszuschlag Jahr</t>
         </is>
       </c>
-      <c r="D30" s="48">
+      <c r="D30" s="49">
         <f>IF(D25&lt;=D29,0,ROUND(MIN(0.055*D25,0.119*(D25-D29)),2))</f>
         <v/>
       </c>
@@ -10157,7 +11298,7 @@
           <t>Solidaritätszuschlag monatlich</t>
         </is>
       </c>
-      <c r="D31" s="48">
+      <c r="D31" s="49">
         <f>ROUND(D30/12,2)</f>
         <v/>
       </c>
@@ -10174,14 +11315,14 @@
           <t>Kirchensteuer monatlich</t>
         </is>
       </c>
-      <c r="D32" s="48">
+      <c r="D32" s="49">
         <f>IF(Настройки!$D$48="ja",ROUND(D26*Настройки!$D$49,2),0)</f>
         <v/>
       </c>
       <c r="E32" s="8" t="inlineStr"/>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="54">
+      <c r="B34" s="55">
         <f>IF(OR(Настройки!$D$47=5,Настройки!$D$47=6),"ВНИМАНИЕ: для классов 5 и 6 действует другой алгоритм (§ 39b Abs. 2 S. 7 EStG) — расчёт НЕ подходит.","Оценка. Официальная сумма — в Lohnabrechnung. Сверить: bmf-steuerrechner.de (там выбери Steuerklasse 3, Kinderfreibetrag 1,0)")</f>
         <v/>
       </c>
@@ -10235,32 +11376,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="55" t="inlineStr">
+      <c r="B4" s="56" t="inlineStr">
         <is>
           <t>Неделя с</t>
         </is>
       </c>
-      <c r="C4" s="55" t="inlineStr">
+      <c r="C4" s="56" t="inlineStr">
         <is>
           <t>по</t>
         </is>
       </c>
-      <c r="D4" s="55" t="inlineStr">
+      <c r="D4" s="56" t="inlineStr">
         <is>
           <t>Часов</t>
         </is>
       </c>
-      <c r="E4" s="55" t="inlineStr">
+      <c r="E4" s="56" t="inlineStr">
         <is>
           <t>Смен</t>
         </is>
       </c>
-      <c r="F4" s="55" t="inlineStr">
+      <c r="F4" s="56" t="inlineStr">
         <is>
           <t>Ночных</t>
         </is>
       </c>
-      <c r="G4" s="55" t="inlineStr">
+      <c r="G4" s="56" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
@@ -10279,11 +11420,11 @@
         <f>SUMIFS(Dienstplan!$L$5:$L$35,Dienstplan!$A$5:$A$35,"&gt;="&amp;B5,Dienstplan!$A$5:$A$35,"&lt;="&amp;C5)</f>
         <v/>
       </c>
-      <c r="E5" s="56">
+      <c r="E5" s="57">
         <f>COUNTIFS(Dienstplan!$A$5:$A$35,"&gt;="&amp;B5,Dienstplan!$A$5:$A$35,"&lt;="&amp;C5,Dienstplan!$L$5:$L$35,"&gt;0")</f>
         <v/>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="57">
         <f>COUNTIFS(Dienstplan!$A$5:$A$35,"&gt;="&amp;B5,Dienstplan!$A$5:$A$35,"&lt;="&amp;C5,Dienstplan!$D$5:$D$35,"ND")</f>
         <v/>
       </c>
@@ -10305,11 +11446,11 @@
         <f>SUMIFS(Dienstplan!$L$5:$L$35,Dienstplan!$A$5:$A$35,"&gt;="&amp;B6,Dienstplan!$A$5:$A$35,"&lt;="&amp;C6)</f>
         <v/>
       </c>
-      <c r="E6" s="56">
+      <c r="E6" s="57">
         <f>COUNTIFS(Dienstplan!$A$5:$A$35,"&gt;="&amp;B6,Dienstplan!$A$5:$A$35,"&lt;="&amp;C6,Dienstplan!$L$5:$L$35,"&gt;0")</f>
         <v/>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="57">
         <f>COUNTIFS(Dienstplan!$A$5:$A$35,"&gt;="&amp;B6,Dienstplan!$A$5:$A$35,"&lt;="&amp;C6,Dienstplan!$D$5:$D$35,"ND")</f>
         <v/>
       </c>
@@ -10331,11 +11472,11 @@
         <f>SUMIFS(Dienstplan!$L$5:$L$35,Dienstplan!$A$5:$A$35,"&gt;="&amp;B7,Dienstplan!$A$5:$A$35,"&lt;="&amp;C7)</f>
         <v/>
       </c>
-      <c r="E7" s="56">
+      <c r="E7" s="57">
         <f>COUNTIFS(Dienstplan!$A$5:$A$35,"&gt;="&amp;B7,Dienstplan!$A$5:$A$35,"&lt;="&amp;C7,Dienstplan!$L$5:$L$35,"&gt;0")</f>
         <v/>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="57">
         <f>COUNTIFS(Dienstplan!$A$5:$A$35,"&gt;="&amp;B7,Dienstplan!$A$5:$A$35,"&lt;="&amp;C7,Dienstplan!$D$5:$D$35,"ND")</f>
         <v/>
       </c>
@@ -10357,11 +11498,11 @@
         <f>SUMIFS(Dienstplan!$L$5:$L$35,Dienstplan!$A$5:$A$35,"&gt;="&amp;B8,Dienstplan!$A$5:$A$35,"&lt;="&amp;C8)</f>
         <v/>
       </c>
-      <c r="E8" s="56">
+      <c r="E8" s="57">
         <f>COUNTIFS(Dienstplan!$A$5:$A$35,"&gt;="&amp;B8,Dienstplan!$A$5:$A$35,"&lt;="&amp;C8,Dienstplan!$L$5:$L$35,"&gt;0")</f>
         <v/>
       </c>
-      <c r="F8" s="56">
+      <c r="F8" s="57">
         <f>COUNTIFS(Dienstplan!$A$5:$A$35,"&gt;="&amp;B8,Dienstplan!$A$5:$A$35,"&lt;="&amp;C8,Dienstplan!$D$5:$D$35,"ND")</f>
         <v/>
       </c>
@@ -10383,11 +11524,11 @@
         <f>SUMIFS(Dienstplan!$L$5:$L$35,Dienstplan!$A$5:$A$35,"&gt;="&amp;B9,Dienstplan!$A$5:$A$35,"&lt;="&amp;C9)</f>
         <v/>
       </c>
-      <c r="E9" s="56">
+      <c r="E9" s="57">
         <f>COUNTIFS(Dienstplan!$A$5:$A$35,"&gt;="&amp;B9,Dienstplan!$A$5:$A$35,"&lt;="&amp;C9,Dienstplan!$L$5:$L$35,"&gt;0")</f>
         <v/>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="57">
         <f>COUNTIFS(Dienstplan!$A$5:$A$35,"&gt;="&amp;B9,Dienstplan!$A$5:$A$35,"&lt;="&amp;C9,Dienstplan!$D$5:$D$35,"ND")</f>
         <v/>
       </c>
@@ -10409,11 +11550,11 @@
         <f>SUMIFS(Dienstplan!$L$5:$L$35,Dienstplan!$A$5:$A$35,"&gt;="&amp;B10,Dienstplan!$A$5:$A$35,"&lt;="&amp;C10)</f>
         <v/>
       </c>
-      <c r="E10" s="56">
+      <c r="E10" s="57">
         <f>COUNTIFS(Dienstplan!$A$5:$A$35,"&gt;="&amp;B10,Dienstplan!$A$5:$A$35,"&lt;="&amp;C10,Dienstplan!$L$5:$L$35,"&gt;0")</f>
         <v/>
       </c>
-      <c r="F10" s="56">
+      <c r="F10" s="57">
         <f>COUNTIFS(Dienstplan!$A$5:$A$35,"&gt;="&amp;B10,Dienstplan!$A$5:$A$35,"&lt;="&amp;C10,Dienstplan!$D$5:$D$35,"ND")</f>
         <v/>
       </c>
@@ -10656,330 +11797,330 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="55" t="inlineStr">
+      <c r="B4" s="56" t="inlineStr">
         <is>
           <t>Тема</t>
         </is>
       </c>
-      <c r="C4" s="55" t="inlineStr">
+      <c r="C4" s="56" t="inlineStr">
         <is>
           <t>Что в договоре</t>
         </is>
       </c>
-      <c r="D4" s="55" t="inlineStr">
+      <c r="D4" s="56" t="inlineStr">
         <is>
           <t>Что по закону / на практике</t>
         </is>
       </c>
-      <c r="E4" s="55" t="inlineStr">
+      <c r="E4" s="56" t="inlineStr">
         <is>
           <t>Что делать</t>
         </is>
       </c>
     </row>
     <row r="5" ht="69" customHeight="1">
-      <c r="B5" s="57" t="inlineStr">
+      <c r="B5" s="58" t="inlineStr">
         <is>
           <t>Einspringprämie</t>
         </is>
       </c>
-      <c r="C5" s="58" t="inlineStr">
+      <c r="C5" s="59" t="inlineStr">
         <is>
           <t>НЕТ НИ СЛОВА. § 4 Abs. 1: любые Sonderleistungen сверх договора — добровольные, права на них нет.</t>
         </is>
       </c>
-      <c r="D5" s="58" t="inlineStr">
+      <c r="D5" s="59" t="inlineStr">
         <is>
           <t>НО § 4 Abs. 1 Satz 3: оговорка о добровольности НЕ действует, если выплата основана на индивидуальной договорённости (individuelle Vertragsabrede). Устная договорённость тоже считается, но её надо доказать.</t>
         </is>
       </c>
-      <c r="E5" s="59" t="inlineStr">
+      <c r="E5" s="60" t="inlineStr">
         <is>
           <t>Напиши руководителю e-mail: «Bitte bestätigen Sie mir die vereinbarte Einspringprämie von … € je kurzfristig übernommenem Dienst.» Ответ по e-mail = доказательство. Без этого премию могут прекратить в любой момент.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="57.5" customHeight="1">
-      <c r="B6" s="57" t="inlineStr">
+      <c r="B6" s="58" t="inlineStr">
         <is>
           <t>Лимит 60 ч переработки</t>
         </is>
       </c>
-      <c r="C6" s="58" t="inlineStr">
+      <c r="C6" s="59" t="inlineStr">
         <is>
           <t>НЕТ ТАКОГО ПРАВИЛА. § 2 Abs. 3 разрешает не оплачивать только 8 ч в месяц. Всё остальное — обычное рабочее время по § 3 Abs. 1 (27 €/ч).</t>
         </is>
       </c>
-      <c r="D6" s="58" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>Замена оплаты на отгулы (Freizeitausgleich) требует соглашения сторон или Betriebsvereinbarung. Работодатель не может ввести это в одностороннем порядке. Часы не пропадают — они на счёте (Arbeitszeitkonto).</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
+      <c r="E6" s="60" t="inlineStr">
         <is>
           <t>Само по себе накопление часов не страшно. Опасен § 14: требуй КАЖДЫЙ месяц письменное подтверждение остатка счёта часов. Это и фиксирует требование, и не даёт сроку истечь.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="57.5" customHeight="1">
-      <c r="B7" s="57" t="inlineStr">
+      <c r="B7" s="58" t="inlineStr">
         <is>
           <t>Ausschlussfrist 3 месяца</t>
         </is>
       </c>
-      <c r="C7" s="58" t="inlineStr">
+      <c r="C7" s="59" t="inlineStr">
         <is>
           <t>§ 14: любые требования пропадают, если не заявлены письменно в течение 3 месяцев с момента, когда они стали к оплате.</t>
         </is>
       </c>
-      <c r="D7" s="58" t="inlineStr">
+      <c r="D7" s="59" t="inlineStr">
         <is>
           <t>Зарплата за август платится 15 сентября → срок по августу истекает 15 декабря. Для перенесённых часов момент возникновения требования спорный — не рискуй.</t>
         </is>
       </c>
-      <c r="E7" s="59" t="inlineStr">
+      <c r="E7" s="60" t="inlineStr">
         <is>
           <t>Достаточно e-mail с формулировкой: «Hiermit mache ich die Vergütung der im Monat … geleisteten … Überstunden geltend.» Храни копию. Это занимает 2 минуты и сохраняет тысячи евро.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="80.5" customHeight="1">
-      <c r="B8" s="57" t="inlineStr">
+      <c r="B8" s="58" t="inlineStr">
         <is>
           <t>12-часовые ночные смены</t>
         </is>
       </c>
-      <c r="C8" s="58" t="inlineStr">
+      <c r="C8" s="59" t="inlineStr">
         <is>
           <t>§ 2 Abs. 2: обязан работать в ночь, в выходные и праздники по распоряжению — «soweit dies gesetzlich zulässig ist».</t>
         </is>
       </c>
-      <c r="D8" s="58" t="inlineStr">
+      <c r="D8" s="59" t="inlineStr">
         <is>
           <t>§ 6 Abs. 2 ArbZG: у ночного работника смена максимум 8 ч, до 10 ч только с компенсацией в течение месяца. 12 ч допустимы лишь при большой доле Bereitschaftsdienst и только на базе тарифа или Betriebsvereinbarung (§ 7 ArbZG). По EzB п. 42 работодатель НЕ tarifgebunden.</t>
         </is>
       </c>
-      <c r="E8" s="59" t="inlineStr">
+      <c r="E8" s="60" t="inlineStr">
         <is>
           <t>Оговорка «soweit gesetzlich zulässig» работает в твою пользу: сверх законного предела ты не обязан. Если давят — Gewerbeaufsichtsamt Hannover. Обращение может быть анонимным.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="57.5" customHeight="1">
-      <c r="B9" s="57" t="inlineStr">
+      <c r="B9" s="58" t="inlineStr">
         <is>
           <t>Ночная надбавка 25 %</t>
         </is>
       </c>
-      <c r="C9" s="58" t="inlineStr">
+      <c r="C9" s="59" t="inlineStr">
         <is>
           <t>§ 3 Abs. 2 a): 25 % за 20:00–06:00.</t>
         </is>
       </c>
-      <c r="D9" s="58" t="inlineStr">
+      <c r="D9" s="59" t="inlineStr">
         <is>
           <t>§ 6 Abs. 5 ArbZG даёт право на «angemessener Zuschlag». BAG: 25 % — норма при обычной ночной работе; при Dauernachtarbeit (как у тебя — почти только ночи) суды присуждали 30 %.</t>
         </is>
       </c>
-      <c r="E9" s="59" t="inlineStr">
+      <c r="E9" s="60" t="inlineStr">
         <is>
           <t>Реальный аргумент на переговорах о повышении. 5 % от 170 ночных часов — это около 230 € в месяц.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
-      <c r="B10" s="57" t="inlineStr">
+      <c r="B10" s="58" t="inlineStr">
         <is>
           <t>Надбавки на переработку</t>
         </is>
       </c>
-      <c r="C10" s="58" t="inlineStr">
+      <c r="C10" s="59" t="inlineStr">
         <is>
           <t>§ 3 Abs. 2: надбавки начисляются «je Stunde auf die (Grund-)Vergütung» — на каждый час, без исключений для переработки.</t>
         </is>
       </c>
-      <c r="D10" s="58" t="inlineStr">
+      <c r="D10" s="59" t="inlineStr">
         <is>
           <t>Значит за переработанные ночные часы надбавка 25 % тоже положена. Частая ошибка расчётчиков — начислить надбавки только на часы в пределах нормы.</t>
         </is>
       </c>
-      <c r="E10" s="59" t="inlineStr">
+      <c r="E10" s="60" t="inlineStr">
         <is>
           <t>Сверь в Lohnabrechnung: количество часов с надбавкой должно совпасть с колонками «Ночь/Воскр./Праздн.» этого файла, а не быть меньше.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="57.5" customHeight="1">
-      <c r="B11" s="57" t="inlineStr">
+      <c r="B11" s="58" t="inlineStr">
         <is>
           <t>Надбавки в отпуске и на больничном</t>
         </is>
       </c>
-      <c r="C11" s="58" t="inlineStr">
+      <c r="C11" s="59" t="inlineStr">
         <is>
           <t>§ 5 и § 6 отсылают к закону.</t>
         </is>
       </c>
-      <c r="D11" s="58" t="inlineStr">
+      <c r="D11" s="59" t="inlineStr">
         <is>
           <t>§ 11 BUrlG: отпускные — среднее за 13 недель ВКЛЮЧАЯ надбавки. § 4 EFZG: больничный — по принципу Lohnausfall, тоже с надбавками за смены по графику.</t>
         </is>
       </c>
-      <c r="E11" s="59" t="inlineStr">
+      <c r="E11" s="60" t="inlineStr">
         <is>
           <t>Проверь: если в месяц с отпуском надбавки резко упали — это ошибка расчёта. Такие надбавки, в отличие от обычных, облагаются налогом (§ 3b требует фактической работы) — файл это учитывает.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
-      <c r="B12" s="57" t="inlineStr">
+      <c r="B12" s="58" t="inlineStr">
         <is>
           <t>Праздники 135 %</t>
         </is>
       </c>
-      <c r="C12" s="58" t="inlineStr">
+      <c r="C12" s="59" t="inlineStr">
         <is>
           <t>§ 3 Abs. 2 d): 135 % за праздник без отгула, 35 % — если дают отгул.</t>
         </is>
       </c>
-      <c r="D12" s="58" t="inlineStr">
+      <c r="D12" s="59" t="inlineStr">
         <is>
           <t>Разница огромная: 12-часовая смена в праздник — 437,40 € надбавки без отгула против 113,40 € с отгулом. Свободны от налога только 125 %, остальные 10 % облагаются.</t>
         </is>
       </c>
-      <c r="E12" s="59" t="inlineStr">
+      <c r="E12" s="60" t="inlineStr">
         <is>
           <t>Заранее уточняй по каждому празднику: с отгулом или без. В файле есть колонка FZA — ставь j (с отгулом) или n (без).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
-      <c r="B13" s="57" t="inlineStr">
+      <c r="B13" s="58" t="inlineStr">
         <is>
           <t>Служебная машина</t>
         </is>
       </c>
-      <c r="C13" s="58" t="inlineStr">
+      <c r="C13" s="59" t="inlineStr">
         <is>
           <t>§ 12 Abs. 1: машина предоставляется, ЛЮБОЕ личное использование запрещено — включая дорогу из дома до места работы.</t>
         </is>
       </c>
-      <c r="D13" s="58" t="inlineStr">
+      <c r="D13" s="59" t="inlineStr">
         <is>
           <t>Раз личного использования нет, нет и geldwerter Vorteil. Правило 1 % применяться НЕ должно.</t>
         </is>
       </c>
-      <c r="E13" s="59" t="inlineStr">
+      <c r="E13" s="60" t="inlineStr">
         <is>
           <t>Проверь Lohnabrechnung: если там есть строка «geldwerter Vorteil Pkw» или «1 %-Regelung» — это ошибка, ты платишь лишний налог и взносы.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
-      <c r="B14" s="57" t="inlineStr">
+      <c r="B14" s="58" t="inlineStr">
         <is>
           <t>Дорога до работы</t>
         </is>
       </c>
-      <c r="C14" s="58" t="inlineStr">
+      <c r="C14" s="59" t="inlineStr">
         <is>
           <t>§ 2 Abs. 5: дорога дом–работа рабочим временем не считается.</t>
         </is>
       </c>
-      <c r="D14" s="58" t="inlineStr">
+      <c r="D14" s="59" t="inlineStr">
         <is>
           <t>Это законно. НО поездки МЕЖДУ пациентами в течение смены — рабочее время и должны оплачиваться.</t>
         </is>
       </c>
-      <c r="E14" s="59" t="inlineStr">
+      <c r="E14" s="60" t="inlineStr">
         <is>
           <t>Если ездишь между объектами — фиксируй это время и требуй оплаты.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="57.5" customHeight="1">
-      <c r="B15" s="57" t="inlineStr">
+      <c r="B15" s="58" t="inlineStr">
         <is>
           <t>Отпуск</t>
         </is>
       </c>
-      <c r="C15" s="58" t="inlineStr">
+      <c r="C15" s="59" t="inlineStr">
         <is>
           <t>§ 5 Abs. 1: «по закону». В EzB стояло 15 дней — но это было для 21 ч/нед.</t>
         </is>
       </c>
-      <c r="D15" s="58" t="inlineStr">
+      <c r="D15" s="59" t="inlineStr">
         <is>
           <t>§ 3 BUrlG при 5-дневной неделе — 20 рабочих дней. Плюс дополнительный оплачиваемый отпуск по PflegeArbbV. При работе по сменам отпуск пересчитывается по фактическим рабочим дням.</t>
         </is>
       </c>
-      <c r="E15" s="59" t="inlineStr">
+      <c r="E15" s="60" t="inlineStr">
         <is>
           <t>Требуй письменного подтверждения количества дней на полной ставке. 15 дней для Vollzeit было бы нарушением закона.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="57.5" customHeight="1">
-      <c r="B16" s="57" t="inlineStr">
+      <c r="B16" s="58" t="inlineStr">
         <is>
           <t>EzB и договор расходятся</t>
         </is>
       </c>
-      <c r="C16" s="58" t="inlineStr">
+      <c r="C16" s="59" t="inlineStr">
         <is>
           <t>EzB от 13.07.2026: 21 ч/нед, 2.184,00 €, старт 15.07.26. Договор от 01.08.2026: 40 ч/нед, 4.676,40 €.</t>
         </is>
       </c>
-      <c r="D16" s="58" t="inlineStr">
+      <c r="D16" s="59" t="inlineStr">
         <is>
           <t>Действует договор — § 18 Abs. 2 прямо заменяет все предыдущие соглашения. Но у Ausländerbehörde в деле лежит версия с 21 часом.</t>
         </is>
       </c>
-      <c r="E16" s="59" t="inlineStr">
+      <c r="E16" s="60" t="inlineStr">
         <is>
           <t>Расхождение между разрешением на работу и фактической занятостью — риск для твоего вида на жительство. Проси работодателя подать новую EzB на полную ставку и оставь себе копию.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
-      <c r="B17" s="57" t="inlineStr">
+      <c r="B17" s="58" t="inlineStr">
         <is>
           <t>Штрафы по договору</t>
         </is>
       </c>
-      <c r="C17" s="58" t="inlineStr">
+      <c r="C17" s="59" t="inlineStr">
         <is>
           <t>§ 9: до одного месячного оклада за нарушение конфиденциальности или невыход на работу. § 17: запрет переманивать сотрудников 24 месяца, тоже месячный оклад.</t>
         </is>
       </c>
-      <c r="D17" s="58" t="inlineStr">
+      <c r="D17" s="59" t="inlineStr">
         <is>
           <t>Такие оговорки часто признают недействительными, но спорить дорого.</t>
         </is>
       </c>
-      <c r="E17" s="59" t="inlineStr">
+      <c r="E17" s="60" t="inlineStr">
         <is>
           <t>Просто знай: увольнение без соблюдения срока = штраф до 4.676,40 €.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
-      <c r="B18" s="57" t="inlineStr">
+      <c r="B18" s="58" t="inlineStr">
         <is>
           <t>Выплата и проверка</t>
         </is>
       </c>
-      <c r="C18" s="58" t="inlineStr">
+      <c r="C18" s="59" t="inlineStr">
         <is>
           <t>§ 3 Abs. 3: 15-го числа следующего месяца, безналично.</t>
         </is>
       </c>
-      <c r="D18" s="58" t="inlineStr">
+      <c r="D18" s="59" t="inlineStr">
         <is>
           <t>Работодатель обязан выдать понятную расчётку (§ 108 GewO) с разбивкой по видам надбавок.</t>
         </is>
       </c>
-      <c r="E18" s="59" t="inlineStr">
+      <c r="E18" s="60" t="inlineStr">
         <is>
           <t>Каждый месяц сверяй расчётку с этим файлом. Расхождение больше пары евро — пиши сразу, не жди.</t>
         </is>
@@ -11016,7 +12157,7 @@
       </c>
     </row>
     <row r="2" ht="34" customHeight="1">
-      <c r="B2" s="60" t="inlineStr">
+      <c r="B2" s="61" t="inlineStr">
         <is>
           <t>ПОЛЯ ОСТАВЛЕНЫ ПУСТЫМИ НАМЕРЕННО: этот файл лежит в публичном репозитории GitHub. Заполни их у себя на телефоне/компьютере и НЕ загружай файл с данными обратно в репозиторий. Steuer-ID и SV-Nummer — это идентификаторы, по которым возможно мошенничество.</t>
         </is>
@@ -11040,7 +12181,7 @@
           <t>Name, Vorname</t>
         </is>
       </c>
-      <c r="D5" s="61" t="inlineStr">
+      <c r="D5" s="62" t="inlineStr">
         <is>
           <t>Karimov, Alisher</t>
         </is>
@@ -11057,7 +12198,7 @@
           <t>Geburtsdatum</t>
         </is>
       </c>
-      <c r="D6" s="61" t="inlineStr">
+      <c r="D6" s="62" t="inlineStr">
         <is>
           <t>07.02.1998</t>
         </is>
@@ -11074,7 +12215,7 @@
           <t>Anschrift</t>
         </is>
       </c>
-      <c r="D7" s="62" t="inlineStr"/>
+      <c r="D7" s="63" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
@@ -11087,7 +12228,7 @@
           <t>Sozialversicherungsnummer</t>
         </is>
       </c>
-      <c r="D8" s="62" t="inlineStr"/>
+      <c r="D8" s="63" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
@@ -11100,7 +12241,7 @@
           <t>Steuer-Identifikationsnummer</t>
         </is>
       </c>
-      <c r="D9" s="62" t="inlineStr"/>
+      <c r="D9" s="63" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
@@ -11113,7 +12254,7 @@
           <t>Krankenkasse</t>
         </is>
       </c>
-      <c r="D10" s="62" t="inlineStr"/>
+      <c r="D10" s="63" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
@@ -11126,7 +12267,7 @@
           <t>Zusatzbeitrag</t>
         </is>
       </c>
-      <c r="D11" s="62" t="inlineStr"/>
+      <c r="D11" s="63" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
@@ -11146,7 +12287,7 @@
           <t>Steuerklasse</t>
         </is>
       </c>
-      <c r="D13" s="61" t="inlineStr">
+      <c r="D13" s="62" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -11163,7 +12304,7 @@
           <t>Kinderfreibeträge</t>
         </is>
       </c>
-      <c r="D14" s="61" t="inlineStr">
+      <c r="D14" s="62" t="inlineStr">
         <is>
           <t>1,0</t>
         </is>
@@ -11180,7 +12321,7 @@
           <t>Kind, geboren am</t>
         </is>
       </c>
-      <c r="D15" s="62" t="inlineStr"/>
+      <c r="D15" s="63" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
@@ -11193,7 +12334,7 @@
           <t>Kirchensteuer</t>
         </is>
       </c>
-      <c r="D16" s="61" t="inlineStr">
+      <c r="D16" s="62" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
@@ -11217,7 +12358,7 @@
           <t>Arbeitgeber</t>
         </is>
       </c>
-      <c r="D18" s="61" t="inlineStr">
+      <c r="D18" s="62" t="inlineStr">
         <is>
           <t>Constantia Intensivpflege GmbH</t>
         </is>
@@ -11234,7 +12375,7 @@
           <t>Anschrift AG</t>
         </is>
       </c>
-      <c r="D19" s="61" t="inlineStr">
+      <c r="D19" s="62" t="inlineStr">
         <is>
           <t>Theaterstraße 1, 30159 Hannover</t>
         </is>
@@ -11251,7 +12392,7 @@
           <t>Betriebsnummer</t>
         </is>
       </c>
-      <c r="D20" s="61" t="inlineStr">
+      <c r="D20" s="62" t="inlineStr">
         <is>
           <t>70027532</t>
         </is>
@@ -11268,7 +12409,7 @@
           <t>Tätigkeit</t>
         </is>
       </c>
-      <c r="D21" s="61" t="inlineStr">
+      <c r="D21" s="62" t="inlineStr">
         <is>
           <t>Examinierte Pflegefachkraft, außerklinische Intensivpflege 1:1</t>
         </is>
@@ -11285,7 +12426,7 @@
           <t>Beginn</t>
         </is>
       </c>
-      <c r="D22" s="61" t="inlineStr">
+      <c r="D22" s="62" t="inlineStr">
         <is>
           <t>01.08.2026</t>
         </is>
@@ -11302,7 +12443,7 @@
           <t>Probezeit</t>
         </is>
       </c>
-      <c r="D23" s="61" t="inlineStr">
+      <c r="D23" s="62" t="inlineStr">
         <is>
           <t>в договоре не предусмотрен</t>
         </is>
@@ -11319,7 +12460,7 @@
           <t>Kontaktperson</t>
         </is>
       </c>
-      <c r="D24" s="61" t="inlineStr">
+      <c r="D24" s="62" t="inlineStr">
         <is>
           <t>Christopher Kruhl · 0511 43834924 · info@constantia-intensiv.de</t>
         </is>

--- a/Gehaltsrechner_Karimov.xlsx
+++ b/Gehaltsrechner_Karimov.xlsx
@@ -816,7 +816,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>График месяца: ND / TD / FREI, статус (Arbeit / Urlaub / Krank), «x» = Eingesprungen. Август 2026 заполнен по факту: 18 смен = 216 ч.</t>
+          <t>График месяца: ND / TD / FREI, статус (Arbeit / Urlaub / Krank), «x» = Eingesprungen. Сейчас заполнен СЕНТЯБРЬ 2026: 10 TD + 5 ND = 15 смен = 180 ч.</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
+    <row r="15" ht="26" customHeight="1">
       <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Сверка с расчёткой</t>
@@ -912,7 +912,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Реальные Lohnabrechnung 07/2026 и 08/2026, разобранные построчно, и проверка каждой суммы.</t>
+          <t>Реальные Lohnabrechnung 07/2026 и 08/2026, разобранные построчно, и проверка каждой суммы. Август зафиксирован числами и не меняется при смене месяца.</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>АВГУСТ — СХОДЯТСЯ ЛИ ЧАСЫ С ГРАФИКОМ</t>
+          <t>АВГУСТ — СХОДЯТСЯ ЛИ ЧАСЫ (числа зафиксированы, лист Dienstplan уже за сентябрь)</t>
         </is>
       </c>
     </row>
@@ -2047,15 +2047,14 @@
     <row r="23">
       <c r="B23" s="64" t="inlineStr">
         <is>
-          <t>Смен по графику (лист Dienstplan)</t>
+          <t>Отработано по графику</t>
         </is>
       </c>
       <c r="C23" s="73" t="n"/>
       <c r="D23" s="73" t="n"/>
       <c r="E23" s="73" t="n"/>
-      <c r="F23" s="75">
-        <f>Dienstplan!$L$36</f>
-        <v/>
+      <c r="F23" s="75" t="n">
+        <v>216</v>
       </c>
       <c r="G23" s="73" t="n"/>
       <c r="H23" s="8" t="inlineStr">
@@ -2112,9 +2111,8 @@
       <c r="C26" s="73" t="n"/>
       <c r="D26" s="73" t="n"/>
       <c r="E26" s="73" t="n"/>
-      <c r="F26" s="75">
-        <f>Dienstplan!$AM$36</f>
-        <v/>
+      <c r="F26" s="75" t="n">
+        <v>132</v>
       </c>
       <c r="G26" s="73" t="n"/>
       <c r="H26" s="8" t="inlineStr">
@@ -2132,9 +2130,8 @@
       <c r="C27" s="73" t="n"/>
       <c r="D27" s="73" t="n"/>
       <c r="E27" s="73" t="n"/>
-      <c r="F27" s="75">
-        <f>Dienstplan!$M$36-Dienstplan!$AM$36</f>
-        <v/>
+      <c r="F27" s="75" t="n">
+        <v>28</v>
       </c>
       <c r="G27" s="73" t="n"/>
       <c r="H27" s="8" t="inlineStr">
@@ -2167,9 +2164,8 @@
       <c r="C29" s="73" t="n"/>
       <c r="D29" s="73" t="n"/>
       <c r="E29" s="73" t="n"/>
-      <c r="F29" s="75">
-        <f>Dienstplan!$N$36</f>
-        <v/>
+      <c r="F29" s="75" t="n">
+        <v>44</v>
       </c>
       <c r="G29" s="73" t="n"/>
       <c r="H29" s="8" t="inlineStr"/>
@@ -2206,7 +2202,7 @@
     <row r="34" ht="52" customHeight="1">
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Работодатель заплатил ЩЕДРЕЕ, чем написано в договоре: § 2 Abs. 3 разрешает не платить первые 8 ч переработки в месяц, но в расчётке оплачены все 216 ч (168 + 48), а не 208. Это +216,00 € брутто в твою пользу. Лист «Расчёт» считает строго по договору, поэтому там брутто 7.101 €, а в расчётке 7.317 €. Если хочешь, чтобы файл повторял расчётку точь-в-точь, поставь в «Настройках» «Переработка включена в оклад» = 0.</t>
+          <t>Работодатель заплатил ЩЕДРЕЕ, чем написано в договоре: § 2 Abs. 3 разрешает не платить первые 8 ч переработки в месяц, но в расчётке оплачены все 216 ч (168 + 48), а не 208. Это +216,00 € брутто в твою пользу. Поэтому в «Настройках» «Переработка включена в оклад» стоит 0 — так файл повторяет расчётку. Поставь 8, если захочешь увидеть, сколько работодатель обязан минимум по договору.</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2757,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="8" t="inlineStr"/>
     </row>
@@ -2904,11 +2900,11 @@
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>§ 2 Abs. 3 — до 8 ч/мес уже в окладе</t>
+          <t>§ 2 Abs. 3 договора разрешает не платить первые 8 ч/мес. Но в расчётке 08/2026 оплачены ВСЕ 216 ч — поэтому здесь 0. Поставь 8, если хочешь увидеть минимум по договору</t>
         </is>
       </c>
     </row>
@@ -4757,10 +4753,14 @@
       </c>
       <c r="D5" s="30" t="inlineStr">
         <is>
-          <t>FREI</t>
-        </is>
-      </c>
-      <c r="E5" s="30" t="inlineStr"/>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="E5" s="30" t="inlineStr">
+        <is>
+          <t>Arbeit</t>
+        </is>
+      </c>
       <c r="F5" s="30" t="inlineStr"/>
       <c r="G5" s="30" t="inlineStr"/>
       <c r="H5" s="31">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="D6" s="30" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="E6" s="30" t="inlineStr">
@@ -5066,14 +5066,10 @@
       </c>
       <c r="D7" s="30" t="inlineStr">
         <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="E7" s="30" t="inlineStr">
-        <is>
-          <t>Arbeit</t>
-        </is>
-      </c>
+          <t>FREI</t>
+        </is>
+      </c>
+      <c r="E7" s="30" t="inlineStr"/>
       <c r="F7" s="30" t="inlineStr"/>
       <c r="G7" s="30" t="inlineStr"/>
       <c r="H7" s="31">
@@ -5540,10 +5536,14 @@
       </c>
       <c r="D10" s="30" t="inlineStr">
         <is>
-          <t>FREI</t>
-        </is>
-      </c>
-      <c r="E10" s="30" t="inlineStr"/>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>Arbeit</t>
+        </is>
+      </c>
       <c r="F10" s="30" t="inlineStr"/>
       <c r="G10" s="30" t="inlineStr"/>
       <c r="H10" s="31">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="D13" s="30" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="E13" s="30" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="D14" s="30" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="E14" s="30" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="D15" s="30" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="E15" s="30" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="D16" s="30" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="E16" s="30" t="inlineStr">
@@ -6634,10 +6634,14 @@
       </c>
       <c r="D17" s="30" t="inlineStr">
         <is>
-          <t>FREI</t>
-        </is>
-      </c>
-      <c r="E17" s="30" t="inlineStr"/>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="E17" s="30" t="inlineStr">
+        <is>
+          <t>Arbeit</t>
+        </is>
+      </c>
       <c r="F17" s="30" t="inlineStr"/>
       <c r="G17" s="30" t="inlineStr"/>
       <c r="H17" s="31">
@@ -6788,10 +6792,14 @@
       </c>
       <c r="D18" s="30" t="inlineStr">
         <is>
-          <t>FREI</t>
-        </is>
-      </c>
-      <c r="E18" s="30" t="inlineStr"/>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="E18" s="30" t="inlineStr">
+        <is>
+          <t>Arbeit</t>
+        </is>
+      </c>
       <c r="F18" s="30" t="inlineStr"/>
       <c r="G18" s="30" t="inlineStr"/>
       <c r="H18" s="31">
@@ -6942,14 +6950,10 @@
       </c>
       <c r="D19" s="30" t="inlineStr">
         <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="E19" s="30" t="inlineStr">
-        <is>
-          <t>Arbeit</t>
-        </is>
-      </c>
+          <t>FREI</t>
+        </is>
+      </c>
+      <c r="E19" s="30" t="inlineStr"/>
       <c r="F19" s="30" t="inlineStr"/>
       <c r="G19" s="30" t="inlineStr"/>
       <c r="H19" s="31">
@@ -7100,14 +7104,10 @@
       </c>
       <c r="D20" s="30" t="inlineStr">
         <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="E20" s="30" t="inlineStr">
-        <is>
-          <t>Arbeit</t>
-        </is>
-      </c>
+          <t>FREI</t>
+        </is>
+      </c>
+      <c r="E20" s="30" t="inlineStr"/>
       <c r="F20" s="30" t="inlineStr"/>
       <c r="G20" s="30" t="inlineStr"/>
       <c r="H20" s="31">
@@ -8028,14 +8028,10 @@
       </c>
       <c r="D26" s="30" t="inlineStr">
         <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="E26" s="30" t="inlineStr">
-        <is>
-          <t>Arbeit</t>
-        </is>
-      </c>
+          <t>FREI</t>
+        </is>
+      </c>
+      <c r="E26" s="30" t="inlineStr"/>
       <c r="F26" s="30" t="inlineStr"/>
       <c r="G26" s="30" t="inlineStr"/>
       <c r="H26" s="31">
@@ -8194,11 +8190,7 @@
           <t>Arbeit</t>
         </is>
       </c>
-      <c r="F27" s="30" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F27" s="30" t="inlineStr"/>
       <c r="G27" s="30" t="inlineStr"/>
       <c r="H27" s="31">
         <f>IF($D27="ND",Настройки!$D$42,IF($D27="TD",Настройки!$D$39,""))</f>
@@ -8348,7 +8340,7 @@
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="E28" s="30" t="inlineStr">
@@ -8506,14 +8498,10 @@
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="E29" s="30" t="inlineStr">
-        <is>
-          <t>Arbeit</t>
-        </is>
-      </c>
+          <t>FREI</t>
+        </is>
+      </c>
+      <c r="E29" s="30" t="inlineStr"/>
       <c r="F29" s="30" t="inlineStr"/>
       <c r="G29" s="30" t="inlineStr"/>
       <c r="H29" s="31">
@@ -8664,14 +8652,10 @@
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="E30" s="30" t="inlineStr">
-        <is>
-          <t>Arbeit</t>
-        </is>
-      </c>
+          <t>FREI</t>
+        </is>
+      </c>
+      <c r="E30" s="30" t="inlineStr"/>
       <c r="F30" s="30" t="inlineStr"/>
       <c r="G30" s="30" t="inlineStr"/>
       <c r="H30" s="31">
@@ -8822,10 +8806,14 @@
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
-          <t>FREI</t>
-        </is>
-      </c>
-      <c r="E31" s="30" t="inlineStr"/>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="E31" s="30" t="inlineStr">
+        <is>
+          <t>Arbeit</t>
+        </is>
+      </c>
       <c r="F31" s="30" t="inlineStr"/>
       <c r="G31" s="30" t="inlineStr"/>
       <c r="H31" s="31">
@@ -8984,11 +8972,7 @@
           <t>Arbeit</t>
         </is>
       </c>
-      <c r="F32" s="30" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F32" s="30" t="inlineStr"/>
       <c r="G32" s="30" t="inlineStr"/>
       <c r="H32" s="31">
         <f>IF($D32="ND",Настройки!$D$42,IF($D32="TD",Настройки!$D$39,""))</f>
@@ -9138,14 +9122,10 @@
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="E33" s="30" t="inlineStr">
-        <is>
-          <t>Arbeit</t>
-        </is>
-      </c>
+          <t>FREI</t>
+        </is>
+      </c>
+      <c r="E33" s="30" t="inlineStr"/>
       <c r="F33" s="30" t="inlineStr"/>
       <c r="G33" s="30" t="inlineStr"/>
       <c r="H33" s="31">
@@ -9296,14 +9276,10 @@
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="E34" s="30" t="inlineStr">
-        <is>
-          <t>Arbeit</t>
-        </is>
-      </c>
+          <t>FREI</t>
+        </is>
+      </c>
+      <c r="E34" s="30" t="inlineStr"/>
       <c r="F34" s="30" t="inlineStr"/>
       <c r="G34" s="30" t="inlineStr"/>
       <c r="H34" s="31">

--- a/Gehaltsrechner_Karimov.xlsx
+++ b/Gehaltsrechner_Karimov.xlsx
@@ -1609,7 +1609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2644,37 +2644,52 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1">
+    <row r="65" ht="39" customHeight="1">
       <c r="B65" s="5" t="inlineStr">
         <is>
+          <t>· Времена надбавок подтверждены работодателем письменно (Chris, WhatsApp, сентябрь 2026): ночь 20:00–06:00, воскресенье с 00:00, и при совпадении воскресенья с ночью считается ВОСКРЕСЕНЬЕ. Именно так файл и считает. Отсюда те 28 часов в августе, что ушли из ночных (25 %) в воскресные (50 %).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="52" customHeight="1">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>· ОТКРЫТО: как оплачивается ПРАЗДНИК. Договор § 3 Abs. 2 даёт +35 % с отгулом (c) или +135 % без отгула (d). Ни одной расчётки с праздником ещё не было. Первый случай — 03.10.2026, Tag der Deutschen Einheit: 12 праздничных часов, разница между вариантами ≈ 324 € брутто. Спросить заранее и проверить строку Feiertagszuschlag в расчётке за октябрь.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="B67" s="5" t="inlineStr">
+        <is>
           <t>· Доп. взнос кассы AOK Baden-Württemberg = 2,99 % (не средние 2,9 %). В «Настройках» исправлено.</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1">
-      <c r="B66" s="5" t="inlineStr">
+    <row r="68" ht="15" customHeight="1">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>· Доплата бездетным в Pflegeversicherung (0,6 %) не удерживается — ребёнок учтён правильно.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="26" customHeight="1">
-      <c r="B67" s="5" t="inlineStr">
+    <row r="69" ht="26" customHeight="1">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>· Надбавки провели полностью свободными от взносов, хотя § 1 SvEV освобождает только с базы 25 €/ч. Сейчас это в твою пользу (~110 € в месяц), но уменьшает будущую пенсию на эту же базу.</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="26" customHeight="1">
-      <c r="B69" s="78" t="inlineStr">
+    <row r="71" ht="26" customHeight="1">
+      <c r="B71" s="78" t="inlineStr">
         <is>
           <t>Сроки, которые нельзя пропустить: по июлю — до 15.11.2026, по августу — до 14.12.2026. Разговор в WhatsApp сроки НЕ прерывает, нужна письменная претензия (e-mail достаточно).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="B65:H65"/>
+    <mergeCell ref="B68:H68"/>
     <mergeCell ref="B64:H64"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="A1:H1"/>
@@ -2687,6 +2702,7 @@
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B66:H66"/>
     <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B71:H71"/>
     <mergeCell ref="B21:H21"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B60:H60"/>
@@ -3073,7 +3089,7 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>20 = 20:00</t>
+          <t>20 = 20:00. Подтверждено работодателем (Chris, WhatsApp 09/2026): «20:00 – 06:00 morgens Nacht»</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3129,7 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>§ 3 Abs. 2 b)</t>
+          <t>§ 3 Abs. 2 b). Подтверждено (Chris): «Sonntags Zuschlag ab 00:00» и «Sonntag &gt; als Nacht, dann zählt Sonntag» — надбавки НЕ складываются</t>
         </is>
       </c>
     </row>

--- a/Gehaltsrechner_Karimov.xlsx
+++ b/Gehaltsrechner_Karimov.xlsx
@@ -816,7 +816,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>График месяца: ND / TD / FREI, статус (Arbeit / Urlaub / Krank), «x» = Eingesprungen. Сейчас заполнен СЕНТЯБРЬ 2026: 10 TD + 5 ND = 15 смен = 180 ч.</t>
+          <t>График месяца: ND / TD / FREI, статус (Arbeit / Urlaub / Krank), «x» = Eingesprungen. Сейчас заполнен СЕНТЯБРЬ 2026: 14 TD + 3 ND = 17 смен = 204 ч.</t>
         </is>
       </c>
     </row>
@@ -8514,11 +8514,19 @@
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
-          <t>FREI</t>
-        </is>
-      </c>
-      <c r="E29" s="30" t="inlineStr"/>
-      <c r="F29" s="30" t="inlineStr"/>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="E29" s="30" t="inlineStr">
+        <is>
+          <t>Arbeit</t>
+        </is>
+      </c>
+      <c r="F29" s="30" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G29" s="30" t="inlineStr"/>
       <c r="H29" s="31">
         <f>IF($D29="ND",Настройки!$D$42,IF($D29="TD",Настройки!$D$39,""))</f>
@@ -8822,14 +8830,10 @@
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="E31" s="30" t="inlineStr">
-        <is>
-          <t>Arbeit</t>
-        </is>
-      </c>
+          <t>FREI</t>
+        </is>
+      </c>
+      <c r="E31" s="30" t="inlineStr"/>
       <c r="F31" s="30" t="inlineStr"/>
       <c r="G31" s="30" t="inlineStr"/>
       <c r="H31" s="31">
@@ -8980,7 +8984,7 @@
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="E32" s="30" t="inlineStr">
@@ -9138,10 +9142,14 @@
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
-          <t>FREI</t>
-        </is>
-      </c>
-      <c r="E33" s="30" t="inlineStr"/>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="E33" s="30" t="inlineStr">
+        <is>
+          <t>Arbeit</t>
+        </is>
+      </c>
       <c r="F33" s="30" t="inlineStr"/>
       <c r="G33" s="30" t="inlineStr"/>
       <c r="H33" s="31">
@@ -9292,10 +9300,14 @@
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
-          <t>FREI</t>
-        </is>
-      </c>
-      <c r="E34" s="30" t="inlineStr"/>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="E34" s="30" t="inlineStr">
+        <is>
+          <t>Arbeit</t>
+        </is>
+      </c>
       <c r="F34" s="30" t="inlineStr"/>
       <c r="G34" s="30" t="inlineStr"/>
       <c r="H34" s="31">

--- a/Gehaltsrechner_Karimov.xlsx
+++ b/Gehaltsrechner_Karimov.xlsx
@@ -816,7 +816,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>График месяца: ND / TD / FREI, статус (Arbeit / Urlaub / Krank), «x» = Eingesprungen. Сейчас заполнен СЕНТЯБРЬ 2026: 14 TD + 3 ND = 17 смен = 204 ч.</t>
+          <t>График месяца: ND / TD / FREI, статус (Arbeit / Urlaub / Krank), «x» = Eingesprungen. Сейчас заполнен СЕНТЯБРЬ 2026: 15 TD + 3 ND = 18 смен = 216 ч.</t>
         </is>
       </c>
     </row>
@@ -8830,10 +8830,14 @@
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
-          <t>FREI</t>
-        </is>
-      </c>
-      <c r="E31" s="30" t="inlineStr"/>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="E31" s="30" t="inlineStr">
+        <is>
+          <t>Arbeit</t>
+        </is>
+      </c>
       <c r="F31" s="30" t="inlineStr"/>
       <c r="G31" s="30" t="inlineStr"/>
       <c r="H31" s="31">

--- a/Gehaltsrechner_Karimov.xlsx
+++ b/Gehaltsrechner_Karimov.xlsx
@@ -816,7 +816,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>График месяца: ND / TD / FREI, статус (Arbeit / Urlaub / Krank), «x» = Eingesprungen. Сейчас заполнен СЕНТЯБРЬ 2026: 15 TD + 3 ND = 18 смен = 216 ч.</t>
+          <t>График месяца: ND / TD / FREI, статус (Arbeit / Urlaub / Krank), «x» = Eingesprungen. Сейчас заполнен СЕНТЯБРЬ 2026: 14 TD + 3 ND = 17 смен = 204 ч.</t>
         </is>
       </c>
     </row>
@@ -8830,14 +8830,10 @@
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="E31" s="30" t="inlineStr">
-        <is>
-          <t>Arbeit</t>
-        </is>
-      </c>
+          <t>FREI</t>
+        </is>
+      </c>
+      <c r="E31" s="30" t="inlineStr"/>
       <c r="F31" s="30" t="inlineStr"/>
       <c r="G31" s="30" t="inlineStr"/>
       <c r="H31" s="31">
